--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,512 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Good Job Games</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://pk.linkedin.com/company/goodjobgames?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>... 51-200 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded: 2017. Locations. Primary. Istanbul, Istanbul, TR. Get directions. Employees ...</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Mavidev Yazılım ve Danışmanlık A.Ş.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mavidev-software</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Website: https://mavidev.com/. External link for Mavidev Yazılım ve Danışmanlık A.Ş. ; Industry: Software Development ; Company size: 11-50 employees.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TLE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tle-software</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Privately Held. Founded: 2019. Specialties: yazılım, teknoloji, savunma sanayii, bilişim, ar-ge, üretim, tms, wms, lojistik yazılım, and software ... İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Proliz Yazilim</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/proliz-yazilim</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Website: http://www.prolizyazilim.com. External link for Proliz Yazilim ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: Ankara, ...</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SDM Yazılım Hizmetleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sdmyazilim</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SDM Yazılım Hizmetleri A.Ş. Software Development. Şişli, İstanbul 4,386 followers. Şirketinizin verimliliğini Özel Yazılım ve Kurumsal Kaynak Planlama ...</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/ak-ay-elektrik</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>... 51-200 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded: 1992. Specialties: HV/MV/LV Substations, MV/LV Distribution Lines, Overhead ...</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IND Software</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ind-yaz-l-m-bili-im-teknolojileri-sanayi-ve-ticaret-a-</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>... web based automation software system and put on the market in July 2012. We ... Istanbul, Istanbul. Show more similar pages. Show fewer similar pages ...</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Code5 Yazılım Otomasyon Sistemleri Ltd. Şti.</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/code5-yaz-l-m</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, Beylikdüzü. Type: Privately Held. Founded: 2004. Specialties: Crm Yazılımı, Gayrimenkul Crm, İnşaat Crm, Web Yazılım ...</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hosti Bilişim</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://az.linkedin.com/company/hosti-bilisim-network-center?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>... Ankara-İstanbul, YENIMAHALLE 9 followers. Follow · Report this company; Close ... Yazılım Hizmetleri, Hosting ve Sistem Hizmetleri, Game Hosting Hizmetleri ...</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Blitz Technology</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/blitztechnology/</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BLITZ TECHNOLOGY is a leading provider of gyro-stabilized gimbal payloads for aerial platforms, offering comprehensive video processing hardware and software solutions developed in-house.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mikro</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mikro-tasarim</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Mikro-Tasarım was founded as an IC design company in November 2008 within the METU Technopolis, a university incubation center for high-tech startups. Mikro-Tasarım provides design services for ...</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Poliark</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/poliark</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Poliark is on a mission to help built environment sector to eliminate workflow inefficiency by providing collaborative instant designs through multimodal AI, KEND, enabling to finish weeks long ...</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unscrambl, Inc</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unscrambl</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Unscrambl, Inc | 9,521 followers on LinkedIn. Changing the way the business users in any enterprise consume data --&gt;have natural language conversations with your data | Unscrambl is an Augmented ...</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TEB Asset Management</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tebportfoy/</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TEB Asset Management Investment Management Farklı yatırımcı ihtiyaçlarına yönelik geniş fon yelpazesi TEB Portföy'de. #İyiKarar</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Garraje</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/garraje</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Garraje is a multi-award-winning 360° digital, public relations, and marketing agency with offices in Istanbul, Miami, Dubai, and Casablanca. We serve clients across diverse industries ...</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WeTransfer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wetransfer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>WeTransfer | 45,405 followers on LinkedIn. The simplest way to send big files? That’s us. | The simplest way to send big files? That’s us. A platform to empower creatives while using business ...</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Atirad Yazılım</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/atirad-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Atirad Yazılım | 177 followers on LinkedIn. Güvenilir ve Etkin Çözümler | Mobil ve Web Tabanlı Uygulamalar, Medical Yazılım, Sistem ve Ağ Çözümleri. ... Ankara, ...</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Volant Yazılım A.Ş.</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/volant-yaz%C4%B1l%C4%B1m-a.%C5%9F.?originalSubdomain=tr</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 11-50 employees. Headquarters: İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sistem Yazılım ve Danışmanlık</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/s%C4%B1stem-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Type: Privately Held. Founded ... Similar pages. İş Yazılım. Software Development. Gölbaşı, Ankara. SMLabs ...</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>N2Mobil Tracking Systems Inc.</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/n2mobil/</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Araç Takip Sistemi, Hafriyat Takip Sistemi, Mobil Kamera Sistemi, Görüntülü İletişim sistemleri, and Yazılım Geliştirme ... Ankara, Çankaya · Trio Mobil. Software ...</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Metaverse Bilişim Yazılım</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metaverse-bili%C5%9Fim-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Kadıköy, İstanbul. Üçgen Yazılım. Software Development. Fika Yazılım. Software Development. Besiktas, Istanbul. Yenasoft Yazılım. Software Development. Akdeniz ...</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Evrim Software and Consulting</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/evrimyazilim</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: ZEYTİNBURNU, İSTANBUL. Type: Partnership. Founded: 1992. Specialties: yazılım , software, ...</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2N TECH</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/2ntechnology</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Modern mobil teknolojilerinde uzman Mobil Uygulama Geliştirme Uzmanları arıyoruz! ... Modern web teknolojilerinde uzman Ön Yüz Yazılım Uzmanları arıyoruz!</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,6 +1858,600 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VAS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vasbilisim</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>... İstanbul. Atasehir, Istanbul 34704, TR. Get directions. Armada İş Merkezi. Eskişehir Yolu No. 6 Kat: 12 Ofis: 1225D6 Söğütözü, 06520. Ankara, TR ... yazılım ...</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mobiversite</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mobiversite</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mobiversite. Software Development. Ankara, Çankaya 15,412 followers. Developing and publishing innovative AI-powered mobile apps used by millions worldwide.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Datasis Yazılım</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/datasis-yazilim-donanim-iletisim-yayincilik-egitim-ve-sinav-hizmetleri</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>İstanbul, Maltepe 34852, TR. Get directions. Employees at Datasis Yazılım ... Web Developer / Datasis Yazılım Donanım… Click here to view Serkan Tişik's ...</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AYKAN CLINIC</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aykan-clinic</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>... İstanbul Yeditepe Üniversitesi'nde öğretim üyesi olarak görev yaptı ve ... 11-50 employees. Type: Privately Held. Founded: 2020. Employees at AYKAN CLINIC.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Persona</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/softwarepersona</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>... Web ... TNC Group Şirketleri bünyesinde, Software Persona tarafından yürütülen Yazılım Mesleki Gelişim Programı'nı başarıyla tamamlamanın mutluluğunu yaşıyorum.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Byersoft Yazılım Güvenlik Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/byersoft</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2-10 employees. Type: Privately Held. Employees at Byersoft Yazılım Güvenlik ... Junior Software Engineer jobs. 233,545 open jobs · Junior Developer jobs.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Codevo</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/codevo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Codevo. Software Development. Çifte Havuzlar, Istanbul 18,447 followers. Follow.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Codevo</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/codevo</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Software Development. Çifte Havuzlar, Istanbul 18,470 followers. Follow · Report this company; Close menu. View all 37 employees. About us. Codevo delivers ...</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Rast Mobile</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rastmobile</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Zeytinburnu, Istanbul. Type: Privately Held. Founded: 2017. Specialties: Angular, Web ...</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Pars ArGe</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pars-arge/</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Sarp Ertürk tarafından kurulan Kocaeli Üniversitesi İşaret ve Görüntü İşleme Laboratuvarı (KULIS: Kocaeli ... 51-200 employees. Headquarters: Kocaeli, İzmit.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Bluestone Worktops</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/bluestone-worktops</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>... 11-50 employees. Headquarters: WILTSHIRE. Type: Self-Owned. Locations. OLD STATION ... İstanbul · House of Worktops. Retail. London Colney, England · Washroom Fit ...</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AYVOS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/ayvos</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: İstanbul, Esenler. Type: Privately Held. Founded: 2015. Specialties: Computer Vision, Deep ...</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EGEMSOFT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/egemsoft</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Industry: Information Technology &amp; Services. Company size: 51-200 employees. Headquarters: İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AppNation</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/appnationco</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://appnation.co. External link for AppNation ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: Istanbul, ...</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Atolye15</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/atolye15/</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İzmir. Type: Public Company. Founded: 2009. Specialties: Application Development, Startup Development, Web Project Development, ...</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Yenaplus</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/yenaplus?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: İstanbul. Type: Privately Held. Founded: 2020. Specialties: yazılım, mühendislik, simülasyon ...</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AKINSOFT</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/akinsoftyazilim</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>... Web Programları, Mobil Programlar, E-Ticaret çözümleri ve E-Dönüşüm ... Software Development. Konya, Selcuklu 11,412 followers. AKINSOFT - Türkiye'nin ...</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Starlang Yazılım</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/starlang</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>External link for Starlang Yazılım. Industry: Software Development. Company size: 11-50 employees. Headquarters: Istanbul, NA. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Inforra Bilgi Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/inforra-bilgi-teknolojileri</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Ataşehir, Istanbul. Type: Privately Held. Founded: 2018. Specialties: SCCM, EXCHANGE, CLOUD, AZURE, OFFICE 365, POWERSHELL, SCRIPT ...</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Smartiks Technology Solutions</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/smartiks-bilgi-teknolojisi-hizmetleri-a.s.?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Smartiks has leading young software engineers specialized in Microsoft and Oracle platforms. Smartiks has increased its expertise in using advanced technology ...</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AMS Accelerate IT</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ams-ai</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMS Accelerate IT | 24,697 followers on LinkedIn. AMS Accelerate IT is an IT recruitment organization with a solid 16 years' experience background. Our clear purpose is helping you grow your ...</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Vawraek Technology</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vawraek/</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Vawraek Technology | 993 followers on LinkedIn. Vawraek Technology | Found in January 2021, Vawraek Studios aims to bring inovation to the video game industry while staying active in the global ...</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Stone Junction</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stone-junction-ltd</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Stone Junction Public Relations and Communications Services Stafford, Staffordshire, 2,215 followers A technical, international and digital B2B PR and marketing agency. We change minds.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Vima</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vimafair</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>This year's edition brings together 150 artists, 30 galleries, and participants from over 20 countries — with exhibitors joining from Athens, Dubai, New York, Rotterdam, Beirut, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>getirfinans</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getirfinans</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>getirfinans | 25,124 followers on LinkedIn. ama ne finans! hesabın iyi faizle her gün kazandırsın, krediyi iyi oranlarla kullan ve harcarken kazan</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Privé Aero Corporation</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/priv%C3%A9-aero</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Privé Aero builded with 15 years aviation industry experiences in Turkey &amp; MEA. Privé Aero Corporation is located in Istanbul/Turkey for supplying airframe and engine components for the world ...</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PeP</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/peplecepte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PeP Financial Services İstanbul, Maslak 4,144 followers 7/24 hesaplı yurt dışı para transferi, yurt dışı alışverişte PeP Visa kartla kur avantajı ve ücretsiz para çekme.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2452,6 +2452,732 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Clemta</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/clemta-support</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Get access to exclusive perks and offers from leading software ... Similar pages. Vircon Legal. Law Practice. Beyoglu, Istanbul. Vircon Group. Software ...</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Skyloop</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/skyloopc</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>View organization page for Tech Istanbul. Tech Istanbul. 25,159 followers ... Software Engineer Intern jobs. 33 open jobs · Full Stack Engineer jobs. 3,136 ...</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Kodluyoruz</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kodluyoruz/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>... software development, front-end web development,, back-end web development, yazılım, kariyer, Frontend, Backend, veribilimi, and nonprofit. Locations. Primary.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TRAILBLU</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trailblu</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>... web apps in minutes – without a single line of code. We test your app for you ... Istanbul, Istanbul · Olympos. Software Development · MINDRIVE. Technology ...</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ingenium Yazılım Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ingenium-yaz%C4%B1l%C4%B1m-limited-%C5%9Firketi</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ingenium Yazılım Limited Şirketi, mobil uygulama ve yazılım çözümleri geliştiren yenilikçi bir teknoloji şirketidir. ... Software Development. İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Nova Yazılım</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/nova-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Nova Yazılım. Software Development. Alanya, Antalya / Alanya 89 followers. Follow.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Divit Digital Video and Image Technologies</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/divit-digital-video-and-image-technologies</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>The company's flagship product had been until now their license plate recognition software ... İstanbul Teknik Üniversitesi To the partners we already work with, ...</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Tende Elektronik Yazılım Mühendislik İletişim Makina ...</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tende-elektronik-yaz%C4%B1l%C4%B1m-m%C3%BChendislik-i%CC%87leti%C5%9Fim-makina-sanayi-ve-ticaret-ltd-%C5%9Fti/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Sincan, Ankara. Type: Privately Held. Founded: 1997. Specialties: Mekanik Tasarım, Elektronik Tasarım ve Üretim, Yazılım ...</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sekom A.S.</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sekom</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ankara Ticaret Merkezi B Blok K: 15 / 70. ANKARA, Çankaya 06650, TR. Get ... #sekom #wearesekom #yazılımcılargünü #yazılım #teknoloji #devlife #software.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Smartup Teknoloji Araştırma ve Geliştirme A.Ş.</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/smartup-teknoloji-ara%C5%9Ft%C4%B1rma-ve-geli%C5%9Ftirme-a-%C5%9F?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Industry: Financial Services. Company size: 11-50 employees. Headquarters: Sultanbeyli, İSTANBUL.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>BPS Yazılım ve Danışmanlık Hizmetleri Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bps-yaz%C4%B1l%C4%B1m-ve-dan%C4%B1%C5%9Fmanl%C4%B1k-hizmetleri-ltd-%C5%9Fti</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul. Type: Privately Held. Founded: 2018 ... Software Engineer. Click here to view Burak Beydilli's profile. Burak Beydilli.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ereteam</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ereteam</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Website: http://www.ereteam.com. External link for Ereteam ; Industry: IT Services and IT Consulting ; Company size: 51-200 employees ; Headquarters: ISTANBUL, ...</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FIXER</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/company/hellofixer?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FIXER | 653 followers on LinkedIn. Software Development Studio | A software development studio that transforms your ideas into digital products.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NovaVision AI</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/novavisionai</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Software Development. London, England 497 followers. Just Make Any Camera ... İstanbul Kalkınma Ajansı desteği ve İstanbul Ticaret Odası ortaklığıyla ...</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ono AI Based HR Platform</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/onoaihr</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ono AI Based HR Platform. Software Development. İstanbul, Istanbul 28,922 followers. Ono AI transforms all HR processes with cutting-edge artificial ...</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>İleti Yönetim Sistemi A.Ş.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/i%CC%87leti-y%C3%B6netim-sistemi</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Industry: IT Services and IT Consulting. Company size: 51-200 employees. Headquarters: Çankaya ...</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Bimar IT Services</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://al.linkedin.com/company/bimar-it-services</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Similar pages. Arkas Holding. Transportation, Logistics, Supply Chain and Storage. Siskon Yazılım &amp; Otomasyon. Software Development ... İstanbul, Şişli. HubX.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ITT ( IT Talent Turkey )</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/itt123/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Levent. Type: Privately Held. Founded ... Software Development. Austin, Texas · BGTS. IT Services and IT Consulting · RDC ...</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Digital Trade A.Ş.</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://bj.linkedin.com/company/digital-trade-a-%C5%9F-?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, İstanbul/Avcılar. Type: Privately Held. Founded: 2015. Specialties: Bilişim, Ar-Ge, and Eticaret. Locations. Primary.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AIForce Sales Labs</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/aiforcesaleslabs</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AIForce Sales Labs Software Development London, Istanbul 22 followers Sales Force Automation powered by AI</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Management@HHU Düsseldorf</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://lc.linkedin.com/company/hhu-management</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Management@HHU Düsseldorf | 2,471 followers on LinkedIn. Lehrstuhl für BWL, insbesondere Management mit Fokus auf Innovation, Strategie und digitales Management | Der Lehrstuhl BWL, insbesondere Management widmet sich in Forschung, Lehre und Praxis aktuellen Themen des strategischen und unternehmerischen Managements. Im Rahmen der Forschung konzentrieren wir uns auf großzahlige empirische ...</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Pretty Picky Properties</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/pretty-picky-properties</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Pretty Picky Properties | 236 followers on LinkedIn. There are a lot of places to rent for a summer vacation on the Lower Cape. There are only a few Pretty Picky Properties. | We specialize in select vacation rentals -- homes and cottages on the Lower Cape, mostly on or very near the beach or distinctive in some other way. Our homeowners love their properties, fastidiously maintain them, and ...</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ROUTIN BİLGİ TEKNOLOJİLERİ A.Ş.</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/routin</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>About us Optimization Solutions Website https://www.routin.com.tr External link for ROUTIN BİLGİ TEKNOLOJİLERİ A.Ş. Industry IT Services and IT Consulting Company size 2-10 employees Headquarters ISTANBUL Type Privately Held Founded 2021</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ASISGUARD</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/asisguard</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ASISGUARD | 31,638 followers on LinkedIn. ASİSGUARD mühendislik kabiliyetleriyle; Elektro- Optik Görüş ve Sınır Güvenliği Sistemleri, Askeri Araç Elektroniği Sistemleri, Döner Kanatlı Silahlı/Silahsız Drone Sistemleri, Ekran Sistem Çözümlemeleri’yle bir kısmı ülkemizde ilk olan, millî ve yerli kritik çözümler geliştirmiştir ASİSGUARD’ın tüm sistemleri (özgün ...</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kolay İK</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://dm.linkedin.com/company/kolayik</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Kolay İK | 55,647 followers on LinkedIn. Kolay helps the world’s leading companies manage their HR management tasks across devices. | Founded in 2015, Kolay İK is a SaaS platform specialized in HR management for companies in all sizes. More than 1.800 companies and 150.000 employees are using Kolay İK today. We offer both fundamental and advanced HR solutions.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Open Toolset Project</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://mp.linkedin.com/company/open-toolset-project/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>An Umbrella Project Including Various Open Source Software Projects | Open Toolset Project is an umbrella project founded in the first quarter of 2020 for hosting a group of open source projects. It aims to develop and share software components, libraries and frameworks to help develop beneficial and qualified software products.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Brik</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onbrik</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Kurumsal eğitimler için mobil bir ... Software Development. Şişli, Istanbul. Codeway. Software Development. Barcelona, Catalonia. Tiko Portugal. Real Estate ...</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Mamentis</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/mamentis</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Mobile Computing Software Products. Company size: 2-10 employees. Headquarters: London. Type: Privately Held. Locations. Primary. London , GB. Get directions ...</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Netsum İleri Bilişim Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/netsum-i%CC%87leri-bili%C5%9Fim-teknolojileri</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: KOCAELİ, KOCAELİ/GEBZE/MUALLİMKÖY. Type: Privately Held. Founded: 1996. Locations. Primary. BİLİŞİM VADİSİ NO:143/5 KAT:7 KAPI_NO: ...</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AKKOÇ TEKNOLOJİ LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/akko%C3%A7-teknoloji%CC%87-ltd-%C5%9Fti%CC%87</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Embedded Software Products. Company size: 2-10 employees. Type: Privately Held ... Similar pages. ABRAMAK Bilgi Teknolojileri. Defense and Space Manufacturing.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Portakal Teknoloji</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/company/portakal-teknoloji</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>We specialize in enterprise services, software engineering, tech-services, and university-industry collaborations. ... 2-10 employees. Headquarters: Ankara.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>EROPA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://mk.linkedin.com/company/eropa</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>... İstanbul'da kurulan firmamız SAP B1 ERP Çözümleri konusunda İstanbul, İzmir ve Gaziantep ofisleriyle, danışmanlık ve yazılım geliştirme hizmeti vermektedir.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Emakin</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/emakin</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Dublin City, Ireland. Type: Privately Held. Founded: 2010. Specialties: bpm, süreç yönetimi ...</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3178,6 +3178,160 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BilgiYazan Eğitim Kurumları</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bilgiyazan</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BilgiYazan Eğitim Kurumları | 310 followers on LinkedIn. Yazılım Eğitimlerinin Doğru Adresi | BilgiYazan yazılım geliştirmek, yazılım eğitimleri düzenlemek ...</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ProManage TR</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/promanagetr</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Locations · Primary. Teknopark İstanbul, Teknopark Bulvarı. No: 1 C1 Blok, Kat:8 Pendik · Antalya Teknokenti, Akdeniz Üniversitesi Kampüsü. ARGE- 1 Binasi No: 1/7.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Bilişim Academy</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bilisimacademy/</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>... Software Training Artificial Intelligence Training Digital Forensics ... Headquarters: Ankara, Yenimahalle Founded: 2019 Company Size: 11-50 employees ...</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>91 Software</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/91-software</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: İstanbul, Şişli. Type: Partnership. Founded: 2011. Specialties: Enterprise Web Applications ...</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CodeMag Yazılım ve Makine Hizmetleri Ltd.Şti.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/codemag</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>11-50 employees. Type: Privately Held. Founded: 2007. Employees at CodeMag ... Software Developer · Click here to view Fatih Sezer's profile. Fatih Sezer. Full ...</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Mobiversite</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://mk.linkedin.com/company/mobiversite</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mobiversite. Software Development. Ankara, Çankaya 15,265 followers. Developing and publishing innovative AI-powered mobile apps used by millions worldwide.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Tribal Worldwide Istanbul</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/tribalistanbul?trk=public_profile_topcard-past-company</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Şişli, Istanbul. Type: Privately Held. Specialties: marketing, advertising, web, digital, and interactive. Locations. Primary.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3332,6 +3332,138 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Alone Software &amp; Technology</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alonesoftware/</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Kartal, İstanbul. Type: Privately Held ... Kadıköy- İstanbul, İstanbul · SysinsyS Yönetim Bilgi Sistemleri A.Ş. Software ...</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Intime Info Yazılım Çözümleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intimeinfo</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 51-200 employees. Headquarters: İstanbul, Üsküdar.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Suit Software Solutions©</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/suitsoftware</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Website: https://suityazilim.com/. External link for Suit Software Solutions© - Suit Yazılım© ; Industry: Software Development ; Company size: 2-10 employees.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Rement Bilgi Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rement-bilgi-teknolojileri</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Rement Bilgi Teknolojileri ulusal ve uluslararası pazarlara, önceden karar verilmiş sektörlerde yazılım ve teknoloji çözümleri üretmek için Ankara 'da ...</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CNR App Yazılım Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cnr-app</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Website: https://www.cnrapp.com. External link for CNR App Yazılım Teknolojileri ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters ...</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Tringle</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tringletech</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, Ataşehir. Type: Privately Held. Founded ... Software Engineer. Click here to view Süleyman Emre Yılmazel's profile ...</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3464,6 +3464,490 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SevenApps</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/7apps</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://sevenapps.co. External link for SevenApps ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Bomensoft</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/bomensoft</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul. Novus. Software Development. Boston, Massachusetts. RapidMule. Software Development. İstanbul, Şişli. Show more similar pages. Show fewer ...</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Detera</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/detera</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Istanbul. Type ... Similar pages. Sade Yazılım ve Danışmanlık. Software Development. Maltepe ...</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STT Yazılım ve Otomasyon AŞ.</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sttechtr</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 2-10 employees. Headquarters: İstanbul, Başakşehir.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PruvaSoft Bilişim Teknolojileri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pruvasoft</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Ankara, Bilkent. Type: Partnership. Founded: 2018 ... Soagen Bilişim Teknolojileri Yazılım ve Danışmanlık A.Ş. Software ...</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FUTURİNO BİLGİ SİSTEMLERİ</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/futurino-e-itim-bili-imi?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Software Development. Farmingdale, New Jersey · MADAME COCO. Retail. Şişli, İstanbul · Mehmet Akif Ersoy Ilkogretim Okulu. Primary and Secondary Education ...</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Tahsilist Yazılım A.Ş</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tahsilistyazilim/</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Software Development. Buyukcekmece, Istanbul · BDM Medya Danışmanlık AŞ. Ankara, Ankara · Daynex Yazılım A.Ş. Information Technology &amp; Services. Esenler, ...</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>RIDEV YAZILIM SİSTEMLERİ LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ridevltd</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Type: Privately Held ... Microsoft şirketinde Yazılım Mühendisi · Click here to view Berat X///////'s ...</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iframeapp</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Type: Privately Held. Founded: 2014. Products. No more previous content. i-frame, Low-Code Development ...</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Cretiora</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cretiora</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>... istanbul, Istanbul · AIFTeam | SAP Business One Certified Partner. Information ... Software Development. Istanbul, Ümraniye · Abekus. E-Learning Providers.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cloudypedia</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cloudypedia/</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cloudypedia IT Services and IT Consulting Oakville, Ontario 7,244 followers Cloudypedia, a Google Cloud Managed Services Provider: G Suite, Google Cloud Platform and Chrome.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Vento Games</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vento-games</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Vento Games | 3,992 followers on LinkedIn. Play Cool, Think Smart | We are passionate about creating engaging and innovative puzzle games that challenge the mind and spark joy in players of all ...</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Carmanah Signs</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carmanah-signs</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Carmanah Signs Appliances, Electrical, and Electronics Manufacturing Calgary, Alberta 1,407 followers Your partner in transforming lottery at retail to deliver exceptional player experiences.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Real Estate Standards Organization (RESO)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/real-estate-standards-organization-reso-/</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Real Estate Standards Organization (RESO) is an independent, nonprofit standards body. RESO was formed to develop data standards and processes that create efficiencies for all participants in real ...</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Lefto Studio</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lefto-studio</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Lefto Studio | 1,029 followers on LinkedIn. Lefto Studio is a small indie game studio from Istanbul, Türkiye. We're currently working on BOMBANANA, a multiplayer co-op bomb defusal game. Still ...</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Bottobo Robotics</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bottobo/</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Bottobo is a robotics company aiming to revolutionize and democratize autonomous mobile robots landscape. We build collaborative AMRs that work in harmony with human workforces. We help ...</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MEDRICS Corp</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/medrics</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Medrics is a global healthtech company transforming the patient journey through a unified, all-in-one Digital Front Door platform. With 45+ modules, ranging from white-label mobile apps and e ...</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Vinter AI Recruitment Platform</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/vinter-me</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Our integrated software allows you to create a bias-free ... Kocaeli Dilovası Organize Sanayi Bölgesi ile iş birliğimizi duyurmaktan mutluluk duyuyoruz!</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>REA TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reateknoloji</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>... Istanbul, İzmir , Manisa and London. It has been founded by technology experts who has endless enthusiasm on software ... web solutions , which also has its ...</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>OCTAPULL</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/octapull/?viewAsMember=true</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: İstanbul, Levent ... Alpata Yazılım ve Teknoloji. Software Development. Eskişehir, odunpazarı ...</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Jupiter Software</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/jupitersoftware</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Jupiter Software | 215 followers on LinkedIn. Jüpiter Yazılım, yenilikçi ... Bu hedefler doğrultusunda iOS ve Android platformunda iş ortaklarına mobil ...</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Passgage</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/passgage/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Besiktas, Istanbul. Type: Privately Held. Founded: 2021. Specialties: Human Resources, ...</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3948,6 +3948,534 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Figensoft</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/figensoft</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Figensoft. Software Development. Istanbul, Türkiye 10,992 followers. The leading mobile technology company of Türkiye. Follow.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Omnitive</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/omnitive</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>About us ; Website: www.omnitive.com. External link for Omnitive ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: Sariyer, Istanbul.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Mükellef</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mukellefco/</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Software Development. İstanbul, Fenerbahçe 14,786 followers. Şirketinizi kurun ... ✨ Yapı Kredi Mobil'den limited veya anonim şirketinizle kurumsal ...</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Onlayer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/onlayertech</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ankara, Ankara 06810, TR. Get directions. Lower Ground Floor 50A Belgrave Road ... İstanbul, Istanbul. EasyCep. Computers and Electronics Manufacturing.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Cimri</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/cimri</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Software Development. Kozyatağı, Istanbul 43,145 followers. En Son Kaça Olur ... Türkiye'nin en çok trafik alan web siteleri sıralamasında 38. sırada yer ...</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ALTAY Yazılım Savunma Endüstriyel Sanayi ve Ticaret ...</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://az.linkedin.com/company/altay-yazilim-savunma-endustriyel?trk=public_profile_experience-item_profile-section-card_image-click</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>IT System Custom Software Development. Company size: 51-200 employees. Headquarters: Kavaklıdere, Ankara. Type: Privately Held. Founded: 1957. Specialties ...</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Analiz Yazılım</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/analiz-yaz%C4%B1l%C4%B1m/</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>| Software Developer | Logo ‏Yazılım… See all employees. Updates. View ... Ankara, Ankara · Ankagis Yazılım A.Ş. Software Development. Ankara, Çankaya ...</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Evreka</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/evrekaco?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Cankaya, Ankara. Type: Privately Held. Founded: 2017. Specialties: Internet of Things, ...</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Olu Studio</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://bj.linkedin.com/company/olu-studio-interior-architecture-and-design</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>... 2-10 employees. Headquarters: Cotonu, Littoral. Type: Privately Held. Founded ... Software Development · DF Concept. Furniture and Home Furnishings ...</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>bitaksi</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitaksi/</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://bitaksi.com. External link for bitaksi ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: İstanbul ; Type ...</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TEGSOFT</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tegsoft</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Website: http://www.tegsoft.com. External link for TEGSOFT ; Industry: Telecommunications ; Company size: 11-50 employees ; Headquarters: Kağıthane, İstanbul ; Type ...</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>beemobs</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beemobs/</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Software Development Team… ... Mobilitenin geleceğini yalnızca araçlarla değil; yazılım, bağlantılı sistemler ve sürdürülebilirlik odağında bütüncül ...</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sail Teknoloji Yazılım Otomotiv LTD.xn</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/sail-teknoloji</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: İstanbul, Şişli. Type: Privately Held. Founded: 2010. Specialties: Web Tabalı Yazılım, canbus ...</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Tein Technology</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/solutions44</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>... Software Development in the area of Added Value Services, Test Engineering ... İstanbul Grand Pera'da gerçekleştirildi. TEİN Teknoloji olarak yer ...</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SnA Consulting</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/sna-consulting</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SnA is also pioneering software-based solutions to complement our advisory ... SnA Consulting, Istanbul, Istanbul, Türkiye. 9 · Like Comment Share · View ...</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Goaltech</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/goaltech</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: London, England. Type: Public Company. Founded ... Goaltech, Ankara, Ankara, Türkiye · 2 · Like Comment Share · Goaltech reposted ...</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Swipeline TR</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/swipelinetr</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Technology, Information and Internet. İstanbul, İstanbul 62,337 followers ... Türkiye'nin parlayan üç sektörü; mobil oyun, mobil uygulama ve yapay zeka ...</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ALJ Finansman A.Ş.</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://ki.linkedin.com/company/aljfinans</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ALJ Finans, hizmet verdiği sektöre yönelik KredimOL mobil uygulaması, e-sözleşme hizmeti gibi inovasyonlarıyla farklılaşmaktadır. ALJ Finansman A.Ş., PERYÖN Türkiye İnsan Yönetimi Derneği üyesi ve TRAI'nin Destekçisidir.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/response-growth-systems-company</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>About us We don't run campaigns. We don't manage agencies. We don't sell media. We build the infrastructure that makes all of it compound. Response is not a marketing agency. It never was. We're an AI-native growth systems company — built for CMOs, CDOs, and founders who've realized the problem isn't their budget, their brief, or their team. It's the architecture underneath everything. At ...</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Youplus Teknoloji Yazılım A.Ş</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/youplus-teknoloji-yaz%C4%B1l%C4%B1m-a-%C5%9F</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Yazılım, dijital dönüşüm ve teknoloji çözümleri alanında yenilikçi yaklaşımlar geliştirerek, ihtiyaçlara özel ve kullanıcı odaklı çözümler sunuyoruz.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>id Software</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/id-software</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>id Software | 46,298 followers on LinkedIn. id – defined by Freud as the primal section of the human psyche; id Software, located in Richardson, Texas, was founded in 1991. From inception to ...</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Agro TV</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://mt.linkedin.com/company/agro-tv</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Agro TV | 10,362 followers on LinkedIn. Tarım televizyonculuğunun "A Takımı" ile sizlerleyiz ! | Agro TV Turkey tarımda bilginin ve medyanın gücünü, sektörün ve çiftçilerin kalkınması için kullanarak gelişen bir medya kuruluşudur.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Rhyton Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/rhytonsolutions</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>At Rhyton Solutions, we help EPC organizations in Oil, Gas, and Petrochemical projects execute faster and with higher control through engineering document governance and workflow automation. We are the creators of PiNOR, an AI-powered Engineering Document Management System (EDMS) built specifically for complex EPC environments — where document delays, uncontrolled revisions, and fragmented ...</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Longline Bilişim Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/longlinebilisim</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Longline Bilişim Teknolojileri | 4,986 followers on LinkedIn. Longline Hep Yanınızda! Kaliteli hizmet anlayışı, özgün ve yenilikçi çözümlerle sizinle. | Longline, 2008 yılında kendi ürün ailesini geliştirme kararı aldı. Pazar araştırmaları, saha ve Ar-Ge çalışmaları sonucunda kendi ürünlerini geliştirmeye başladı. İlk etapta üretmeye karar verdiği SFP ...</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4476,6 +4476,248 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DaBNet Bilişim</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dabnet-bili%C5%9Fim</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ANKARA, Balgat/ Çankaya · Efilli. Software Development. Istanbul, Istanbul · Blueit. Software Development · Bend Bilişim. Information Technology &amp; Services ...</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>HR&amp;Tomorrow</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/hrandtomorrow?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>... Web Service Applications - Attendance Tracking Systems – Time and Attendance ... Mobil İmza, Mobil Aplikasyon, Devam Takip Sistemleri, PDKS, Bağlılık ...</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Medila Mobil Sağlık</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/medilamobilsaglik</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Medila Mobil Sağlık | 1966 followers on LinkedIn. İstanbul ve Edremit Körfezi'nde yerinde; online ... Lead Software Engineer Medila Mobil… Click here to view ...</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Faprika</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/faprikacom</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>E-ticaret alanına yeni giren müşterilerimizin yazılım ihtiyaçlarını ... 11-50 employees. Headquarters: BAŞAKŞEHİR, İstanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Artı365 Danışmanlık Hiz. A.Ş.</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/arti365-danismanlik?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Kadıköy, İstanbul. Type: Privately Held. Founded: 2017. Specialties: SGK Teşvikleri, Bordro Danışmanlığı, İnsan Kaynakları ...</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Dante Teknoloji</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/dante-teknoloji/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Sivusto: http://www.danteteknoloji.com. External link for Dante Teknoloji ; Toimiala: Ohjelmistokehitys ; Yrityksen koko: 2-10 employees ; Päätoimipaikka: İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Siber Güvenlik Web TR</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/siber-g%C3%BCvenlik-web-tr</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, TR. Type: Self-Employed. Founded: 2019 ... Mobil Dijital Gençlik Merkezimizde, siber güvenlik eğitimlerimiz tüm hızıyla ...</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ITU Perceptron</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ituperceptron</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>About us ; Industry: Software Development ; Company size: 11-50 employees ; Type: Nonprofit ...</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Infonal</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/infonal</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Infonal is a technology services and IT consultancy company providing deeply enterprise software architecture and domain specific know how. ... ISTANBUL, İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>EXENTECH</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/exentech</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>11-50 employees ... Savunma, Medikal, Havacılık, Endüstriyel Tasarım, Yazılım, Gömülü Sistemler, Bilişim, Haberleşme Sistemleri, and Mobil Uygulamalar ...</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ArdicLabs</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/ardiclabs</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>... Ankara Technology City with support of Turkish Science and Technology ... 11-50 employees. Headquarters: ANKARA, Cankaya. Type: Privately Held. Founded: 2017 ...</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4718,6 +4718,226 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AHK Türkiye</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ahkturkiye</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AHK Türkiye | German-Turkish Chamber of Commerce and Industry Non-profit Organizations İstanbul, Esentepe- Şişli 25,365 followers #AHKTürkiye</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Omer Istanbul Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/omeristanbultr</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>OMER ISTANBUL Dental Clinic is an award-winning dental clinic based in Istanbul, Turkey, providing advanced cosmetic and restorative dentistry for patients from around the world.</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Elektroland Defence</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/elektroland-defence</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Company size 51-200 employees Headquarters ANKARA, GÖLBAŞI Type Privately Held Founded 1996 Specialties Robotik Sistemler, İnsansız Kara Araçları, Mobil Platform, Elektronik, Mekanik, and ...</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Andasis Elektronik Sanayi ve Tic. A.S.</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/andasiselektroniksanayivetic.a.s.</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Andasis Elektronik Sanayi ve Tic. A.S. | 18,255 followers on LinkedIn. Şirketimiz savunma, endüstri, otomotiv sektörlerinde haberleşme ve kontrol ürünlerinin tasarımını yapmaktadır.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Tarentum AI</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tarentum-ai</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tarentum AI Software Development İstanbul, Maslak 4,211 followers Boosting profits of energy &amp; gaming companies with AI</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>L35 Architects</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/l35-arquitectos</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>L35 Architects is an international architecture, urbanism, and design firm with offices in Barcelona, Madrid, Paris, Milano, Miami, Mexico, Bogotá, Santiago, Istanbul, and Abu Dhabi.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Bookyourdata</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bookyourdata.com</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Bookyourdata is a B2B contact data platform ranked #1 by G2 and trusted by 20,000+ paying customers, including teams at Oracle, Carlisle, Allianz, Randstad, Manpower, Harvard, McKinsey, McLaren ...</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ABM Makine A.Ş</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/abm-makine-a-</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>... Istanbul · ARCAN Machinery. Machinery Manufacturing. IZMIR, CIGLI · CTS Makina A.Ş ... Kocaeli, Çayırova · YILMAZ MACHINE. Machinery Manufacturing. İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Ticimax</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/ticimax</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>About us ; Website: www.ticimax.com. External link for Ticimax ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: İstanbul, Ataşehir.</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SmartInfo Data Solution</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/smartinfo-software</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.smartinfo.com.tr. External link for SmartInfo Data Solution ; Industry: Software Development ; Company size: 51-200 employees.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4938,6 +4938,160 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>VNS Teknoloji</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vns-teknoloji</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>İstanbul. Type: Privately Held. Founded: 2024. Specialties: Kurumsal Yazılımlar, Web Teknolojileri (.Net,React), Blockchain Teknolojileri, and Mobil Yazılım ...</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>IONTEGRA YAZILIM</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iontegra-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Software Developer. See all employees. Updates. View organization page for ... yazılım çözümüdür. IONTEGRA WMS, envanter yönetimi ve sipariş karşılama ...</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Tingz</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/tingznet</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: London. Type: Privately Held. Founded: 2019 ... We're #hiring a new Senior Software Engineer in Istanbul. Apply today or ...</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Markakod Reklam Tasarım ve Yazılım Hizmetleri</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/markakod-interactive?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul, Kadıköy. Type: Privately Held. Founded: 2008. Locations. Primary. 19 Mayıs Mahallesi Atatürk Caddesi. Ulyan Engin ...</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Codeliman Bilgi Teknolojileri ve Danışmanlık</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/codeliman</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>... software solutions. We are a team who feels confident to be creative ... Istanbul, İstanbul. KoçSistem. IT Services and IT Consulting. ISTANBUL, TURKIYE ...</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>pratech</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pra-tech</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Kocaeli, Gebze. Rementist :: Öğrenci ve Yeni Mezun Odaklı Sosyal Kariyer Ağı. Technology, Information and Internet. Ankara, Ankara. WorkyBe. Software ...</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>turkpin</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/turkpin</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Bursa, Bursa. Type: Public Company. Founded: 2002. Locations. Primary. Altınova Mh. İstanbul Cd. ... Software Development. Sakarya ...</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D212"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5092,6 +5092,380 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PlusMinusOne</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://mt.linkedin.com/company/plusminusone-inc?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>... software engineers, and data nerds who are dreaming of shaping the future of ... İstanbul, Istanbul. Trendyol Group. Technology, Information and Internet.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Ticimax</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ticimax/</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>... software, special e-commerce solutions and design services. Ticimax helps ... 51-200 employees. Headquarters: İstanbul, Ataşehir. Type: Privately Held ...</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Menulux</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/menulux</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Bu yolculuğun en önemli parçalarından biri olan yazılım ... Software Development. Başiskele, Kocaeli · KerzzPOS. Software Development. İstanbul, İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>AI Agent TR</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aiagenttr</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>We're #hiring a new Senior Data Scientist (Relocation to Dubai) in Istanbul. ... Software Development. San Francisco, California. CloudBees. Software ...</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Vadi Kurumsal Bilgi Sistemleri</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/vadi-kurumsal-bilgi-sistemleri</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>... web tarayıcısından ve donanımdan bağımsızlıktır. Vadi tarafından ... Software Development. İstanbul, Esenler 626 followers. Yerel Yönetim Bilgi Sistemi ...</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Vuvy</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vuvy/</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>About us ; Website: vuvy.com. External link for Vuvy ; Industry: Mobile Gaming Apps ; Company size: 11-50 employees ; Headquarters: İstanbul ; Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Vispection</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vispection</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>About us ; Website: www.vispection.com. External link for Vispection ; Industry: Software Development ; Company size: 2-10 employees ; Type: Privately Held ...</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Mertech Elektronik Arge</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mertech-elektronik-ar-ge-sanayi-ticaret-a-%C5%9F</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>... yazılım platformunu ve farklı patent süreçlerinde olan donanım ürünlerini ... İSTANBUL/ ÇEKMEKÖY, İSTANBUL · OZDISAN ELEKTRONİK SAN. TİC. A.Ş. Appliances ...</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>FinMaks Finansal Teknolojiler A.Ş.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/finmaks</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Sanayi, Istanbul. Type: Privately Held. Founded ... Ankara, Ankara. FinMax. Financial Services. TOM. Financial Services. Üsküdar ...</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>RST A.Ş.</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rst-a-s/</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>... Software, hardware and System Design/Integration Development of System ... 11-50 employees. Headquarters: Ankara. Type: Partnership. Founded: 2012.</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Tridem Yazılım Otomasyon Ar</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/tridem-yaz%C4%B1l%C4%B1m-otomasyon-ar-ge-m%C3%BCh-ve-dan-ltd-%C5%9Fti</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Laitteiden, sähkölaitteiden ja elektroniikan valmistus. Ankara, Çankaya 214 seuraajaa ... 2-10 employees. Päätoimipaikka: Ankara, Çankaya. Tyyppi: Self-Employed.</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Entranet Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/entranetcom</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: London, England. Type: Privately Held ... Web &amp; Mobil Atölye ile kod bilgisine ihtiyaç duymadan modern, SEO uyumlu ve mobil ...</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CloudCan</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/cloudcan</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CloudCan. Information Technology &amp; Services. İstanbul, Maslak 2,360 followers. With our 20 years of technology know-how, we integrate ...</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Erguvan</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/erguvan</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>11-50 employees ... Sarıyer, İstanbul 34485, TR. Get directions. Employees at Erguvan. Click here to view Demircan Çelebi's profile. Demircan Çelebi. Software ...</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>One Eye Systems LC.</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/oneeyesystems</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 11-50 employees. Headquarters: London, England.</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Artron Tasarım</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/artron-tasar%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Ankara. Type: Privately Held. Founded: 2011. Specialties: Avionics Systems. Locations. Primary. Üniversiteler Mahallesi 1596.</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Livinsoft</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/livinsoft</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Livinsoft. Software Development. Istanbul, Kadikoy 304 followers. Cloud-based property management software. Follow.</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D229"/>
+  <dimension ref="A1:D233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5466,6 +5466,94 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Farmazon</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farmazon</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Founded in 2016 as the first B2B marketplace for pharmacies, Farmazon is the leading software company with a vibrant community representing over 95% of all pharmacists in Turkey — and counting ...</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Dataroid</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dataroid/</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Dataroid Product Analytics Software Dataroid is an AI-powered, enterprise-level digital analytics and customer engagement platform that allows companies to measure customer interactions and ...</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>TrioTech Yazılım Ltd.Şti.</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triotech-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Website: http://www.triotech.com.tr. External link for TrioTech Yazılım Ltd.Şti. ; Industry: Software Development ; Company size: 2-10 employees ; Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Troc Yazılım ve Bilişim Sistemleri</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/troc-yaz%C4%B1l%C4%B1m-ve-bili%C5%9Fim-sistemleri</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>İstanbul , sancaktepe. CS-TECH. Defense and Space Manufacturing. Ankara, Ankara. HRINNO. IT Services and IT Consulting. IBSS Technology and Software. IT ...</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D233"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5554,6 +5554,50 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Callmetric AI</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/callmetric-ai</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>About us ; Website: callmetricai.com. External link for Callmetric AI ; Industry: Software Development ; Company size: 2-10 employees ; Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Locksmith Software Technologies</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/locksmith-software-technologies</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Locksmith Software Technologies, with two district offices located in Istanbul and Ankara ... LST Yazılım olarak yapay zekâ destekli kurumsal çözümlerimizi ...</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D235"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5598,6 +5598,314 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Somera</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/somera</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, Kadıköy. Type: Privately Held. Founded ... Ankara, Çankaya 06800, TR. Get directions. İzmir Teknoloji Geliştirme ...</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Miltron</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/miltron-engineering</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Miltron. Defense and Space Manufacturing. Ankara, Çankaya 2,163 followers. Integrated Software Solutions for Critical Industry Applications. Follow.</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Garaj X TEKMER</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/garajx</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Garaj X TEKMER. Software Development. Follow · Report this company; Close ... Ankara and one in Istanbul. Bring one real problem you are stuck on. Someone ...</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Fiber Yazılım</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fiber-yaz-l-m</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Software Development. İstanbul, Şişli 28 followers. Follow · Report this ... Web ve Mobil Yazılım ağırlıklı olarak çalışmaktadır. Aynı zamanda Teknoloji ...</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ZentrumHub</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://dm.linkedin.com/company/zentrumhub/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ZentrumHub | 9,080 followers on LinkedIn. AI-enabled Hotel Booking Platform: Booking Engine, Supplier Connect, White Label, Agent Onboarding | ZentrumHub is a pioneering AI-powered travel technology platform transforming how OTAs, TMCs, and travel businesses connect with global hotel inventory. Founded in 2021 in Pune, India, we serve growing travel agencies worldwide. Our Mission: Become the ...</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Drop Engineering</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/drop-engineering</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Drop Engineering Ltd. is an Istanbul-based company specializing in aerospace, automotive, defense industries. Currently, with expert consulting team, the company serves in different branches such as finite element analyses, testing in high speed deformation of materials (SHPB Systems) and software development for composite manufacturing devices.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Exely</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://uz.linkedin.com/company/exely</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Exely is hospitality software built on a simple belief: your success is our success. We help hotels drive direct sales and maximize occupancy through a single window. From onboarding to growth, we lead you every step of the way. 6,000+ properties across 65+ countries already trust Exely to grow their direct revenue. Top rated on HotelTechReport. Trusted by independent hotels, boutique ...</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Faydam Innovation</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://mk.linkedin.com/company/faydam</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Faydam Innovation | 851 followers on LinkedIn. More accessible and more advanced technology. | Faydam Innovation, in its journey that began in 1998, has introduced numerous technological innovations to the use of our country and the private sector in the Türkiye. In this journey, we have always served and benefited the innovative and open-minded institutions that believed in and supported us ...</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Involit</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://gu.linkedin.com/company/involitbilisim</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Involit | 750 followers on LinkedIn. ITSM, Agile&amp;DevOps, PPM, Work Management, Atlassian, Jira | Firmamız organizasyonlar ölçeğinde mimari çözüm önerileri de sunan, savunma sanayii, yazılım, otomotiv, emlak, üretim, e-ticaret, finans, bankacılık, sigorta, teknoloji, üretim gibi farklı sektördeki müşterilerimize Atlassian ürünlerini enstrüman olarak kullanıp (gerekli ...</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Simternet, Inc</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://at.linkedin.com/company/simternet</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Simternet is a leading Microsoft Gold Certified ISV that develops solution-oriented, web and mobile based applications with more than 20 years of expertise. Simternet offers Digital Workplace Platform for Corporate Communications, HR, IT, Marketing departments of companies with more than 50 employees.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SNI</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/snitechnology</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SNI | 36,161 followers on LinkedIn. Your global tax technology partner | SNI is a Computer Technology Corporation providing Tax Compliance and Regulatory Reporting softwares, interfaces and technologies around the world. As the world&amp;#39;s leading end-to-end Tax Technology provider, SNI is chosen by well-known brands such as Nike, Nestle, Kerry, Deloitte, Geberit, Alcatel, Ferrero and 750 ...</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Yıldız Tech</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/yildiz-tech</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Kısıklı, Istanbul. Type: Privately Held ... Software Architect jobs. 146,015 open jobs · Director jobs. 1,220,357 open jobs ...</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Yazılım Atölyesi</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://az.linkedin.com/company/yazilimatolyesi?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Website: https://yazilimatolyesi.app/#/. External link for Yazılım Atölyesi ; Industry: E-Learning Providers ; Company size: 2-10 employees ; Headquarters: Ankara.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>EVAM</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/evamtech</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Software Development. Istanbul, Istanbul 28,242 followers. A leading ... 51-200 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:D279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5906,6 +5906,666 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>TRUBA</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/truba</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TRUBA | 1,325 followers on LinkedIn. Turkish National Science e-Infrastructure | TÜBİTAK ULAKBİM High Performance and Grid Computing Center is a national center providing high performance computing and data storage for all research institutions and researchers in our country. This center is referred to as the Turkish National e-Science e-Infrastructure (TRUBA) with the decree of the ...</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Domain Reseller</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/company/domain-name-reseller</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Domain Name API is a leading ICANN-accredited domain registrar and reseller platform, founded by Atak Domain Aş. to empower the global domain industry. Our journey began at the Kocaeli University Technology Park, and through continuous innovation, we have grown into a powerhouse supporting 40,000+ partners across 200+ countries. We provide a robust, secure, and highly scalable infrastructure ...</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CodeThreat</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://cg.linkedin.com/company/codethreat/</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>CodeThreat is an AI AppSec platform that acts like your autonomous security engineer. It eliminates false positives, performs contextual SAST analysis using multi-agent LLM models, and integrates seamlessly into modern CI/CD workflows. CodeThreat empowers engineering teams to detect business logic flaws, review pull requests, and ship secure code — fast. Deploy it as SaaS or On-Prem. Build ...</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Inspark Intelligent Business Solutions</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/insparkintelligentbusinesssolutions</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>INSPARK is an independent firm of consultants founded in 1990 in London, operating throughout Europe, combining knowledge, excellence and a strong belief in providing services suitable to customer budget. Extensive and growing knowledge base, results from years of international software implementation resulting in increased quality and customer satisfaction. Our Istanbul, Turkey office covers ...</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Doğa Yazılım ve Bilişim Hizmetleri</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dogayazilim/</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Doğa Yazılım ve Bilişim Hizmetleri Software Development Kocaeli, Çayırova 2,152 followers Büyüyen Şirketler İçin Analitik Raporlama Çözümleri</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>inventures</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://zm.linkedin.com/company/inventures-</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Inventures is the leading early-stage digital business accelerator in Istanbul, driving the success of startups in the dynamic EMEA ecosystem. With a track record of successful exits and a strong network, we provide startups with the resources and support they need to thrive in the competitive digital landscape.</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Devatek Bilgi Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://lt.linkedin.com/company/devatek</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Devatek Bilgi Teknolojileri tarafından geliştirilen Unideva; KOBİ’ler ve mali müşavirler için masaüstü, web ve mobil ortamda kullanılabilen bütünleşik bir muhasebe ve e-dönüşüm uygulamasıdır. Unideva ile süreçlerinizi birlikte değerlendirmek ve size uygun demo akışını planlamak için bizimle iletişime geçebilirsiniz.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Ruul</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/ruul</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Malmö. Type: Privately Held. Founded: 2017 ... Istanbul, Istanbul 34475, TR. Get directions. Narva mnt 5. Tallinn, 10117, EE.</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>NOZZLE</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://ug.linkedin.com/company/nozzle-ship-management-software</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Ataşehir. Type: Privately Held. Founded ... NOZZLE - Ship Management Software, Istanbul, Istanbul, Türkiye · 3 · Like ...</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Koç Bilgi ve Savunma Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/koc-bilgi-ve-savunma-teknoloji?trk=public_profile_experience-item_profile-section-card_subtitle-click</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Ankara, Üniversiteler Mah. Type: Privately Held. Specialties: Aktif/Pasif Sonar Sistemleri, Sensör Verisi İşleme, Karar Destek ...</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Peoplise</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/peoplise/</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: İstanbul. Type: Privately Held. Founded: 2013. Specialties: Recruiting Software, Digital ...</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>MC TEK Bilişim Ltd Şti.</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/mc-tek-bili%C5%9Fim-ltd-%C5%9Fti-</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Ankara, Çankaya. Type: Privately Held. Founded: 2013. Specialties: GIS, Mobile, WEB, Open Source, RFID, QGIS, MDM, and Harita ...</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Pusula Kurumsal İş Çözümleri</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/pusulakurumsal</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Pusula Kurumsal İş Çözümleri. Software Development. Maltepe, Istanbul 12,251 followers. Veri ile Yaşam Bağı Kuruyoruz! See jobs Follow.</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>RTC</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/rtcsuite</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>... software, Compliance Management Solutions, VAT Filling, VAT, Intra-community ... Istanbul, TR. Get directions. SNCF Station 14 rue de Dunkerque. Paris ...</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>BTS Group</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/btsgroup</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>... software-defined everything and autonomous revolution ... Ankara'da bir araya geliyor. BTS Group olarak, 12-15 Mayıs tarihleri ...</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Burdayım App</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/burdayim-app</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, Levent. Type: Privately Held. Founded ... Software Development. Istanbul, Turkiye · TAB Gıda. Restaurants. İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Nesil Teknoloji A.Ş.</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://ne.linkedin.com/company/nesilteknoloji/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: ANKARA. Type: Privately Held. Founded: 2003 ... web sitenizin hangi verileri toplandığını, ne şekilde saklandığını ve ne için ...</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Oobeya, Inc.</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oobeya</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 11-50 employees. Headquarters: Wilmington, Delaware.</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ENKA Systems</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enkasystems/</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>... software products for ENKA Group companies and in the marketing and sale of ... 11-50 employees. Headquarters: Beşiktaş, İstanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Ase Teknoloji Grup</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ase-teknoloji-grup</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Muğla, Bodrum. Type: Privately Held. Founded: 2004 ... Software Engineer jobs. 300,699 open jobs. More searches. More searches.</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Kariyer Mimarı Bilişim Teknolojileri Akademisi</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/kariyer-mimar-bili-im-teknolojileri-akademisi?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Bahçeşehir, İstanbul. Type: Educational. Founded: 1997. Specialties: Microsoft Sistem Eğitimleri, Sanallaştırma Eğitimleri, Ağ ve ...</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Cloud4Next</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/cloud4next</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Samsun'da başlayan yolculuk, yalnızca bir kurtuluş mücadelesi değil ... Software Development. Dover, Delaware · OREDATA. Information Technology &amp; Services.</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Teusan Technology and Space Industry Inc.</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/teusan?trk=public_profile_experience-item_profile-section-card_image-click</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Industry: Aviation &amp; Aerospace. Company size: 11-50 employees. Headquarters: İstanbul, Küçükçekmece.</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Finex Soft</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/finex-soft</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Working on developing stable, high performance and secure web/mobile application, software solutions and products for our customers. ... 2-10 employees.</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Wodo Network</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/wodonetwork</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Zug, ZG Switzerland. Type: Privately Held. Founded: 2021. Specialties: Web 3.0, Game Development, Finance, Software ... Istanbul, ...</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Huzur Faktoring A.Ş</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/huzur-faktoring-a-s</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>... İstanbul'da İkitelli ve Pendik şubeleri ile Adana, Afyonkarahisar, Ankara, Antalya ... Samsun, Trabzon, Kayseri, Konya, Manisa Mersin, Diyarbakır şubeleri ...</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>PraPazar</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/prapazar</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: istanbul, türkiye ... Detaylı bilgi ve canlı demo için web sitemizi ziyaret edebilirsiniz: www.</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Getmobil</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getmobil/</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul, Kağıthane. Type: Privately Held ... Enes Aydın. Vice President of Software Engineering… See all employees. Updates.</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Alarge</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/alarge</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>... software from engineering branches. Alarge employs engineers who are experts ... İstanbul, İstanbul/Esenler · FEV Türkiye. Motor Vehicle Manufacturing · SDM ...</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>PQM</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/pqm-quality-excellence</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: London, England. Type: Privately Held. Founded: 2020. Specialties: QMS, Quality Management System, Manufacturing Software, ...</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D279"/>
+  <dimension ref="A1:D309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6566,6 +6566,666 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>StockMount</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/stockmount</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Ankara, Çankaya ... Bugün, bağımsızlık meşalesinin Samsun'da yakıldığı gün! Gazi Mustafa Kemal ...</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CMS Wise</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/cms-wise-enterprise</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, Kadıköy. Type: Privately Held. Founded ... Software Development. San Clemente, California · Accurace. Data ...</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Kartaca</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://lc.linkedin.com/company/kartaca/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>... mobil servisler, mobil uygulama, sadakat programı, bulut ... Software Development. Innovance Consultancy. IT Services and IT Consulting. Maslak, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>dataliva</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dataliva/</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>... software for the needs of the sector. As Dataliva Information Services, we ... 51-200 employees. Headquarters: İstanbul. Type: Privately Held. Founded: 2015.</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ALATSU</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/company/alatsu-trading</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Gazimagusa, Gazimagusa. Type: Privately Held. Founded: 2018. Specialties: Web ... Senior Software Developer Team Lead. Click here to ...</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>FERFECİR REKLAM AJANSI</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ferfecirreklamajansi</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>FERFECİR REKLAM AJANSI. Advertising Services. İstanbul, Istanbul 1,799 followers ... 11-50 employees. Headquarters: İstanbul, Istanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ISIS Consultancy Education Ltd</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://mk.linkedin.com/company/isisdanismanlik</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ISIS Consultancy Education Ltd. Software Development. İstanbul, Maltepe ... Istanbul, Istanbul konumunda yeni bir SAP FI Danışmanı / SAP FI Consultant ...</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Blitz Technology</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/blitztechnology?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>... software solutions developed in-house. Unlike ... Pendik, Istanbul konumunda yeni bir Kıdemli Gömülü Yazılım Mühendisi için işe alım yapıyoruz #hiring.</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>MobileOcean</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mobileocean/</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: Sariyer, Istanbul. Type: Partnership. Locations. Primary. Sariyer, Istanbul 34396, TR. Get ...</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Hidroan Ankara</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/hidroanankara?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>... mobil hidrolik alanında faaliyet gösteren firmalara projelendirme, satış ve ... 51-200 employees. Headquarters: Ankara, Ostim. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Orphex</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/orphex</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: London ... Similar pages. Academy Club. Professional Training and Coaching. Maslak, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Webrazzi</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/webrazzi</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, TR. Type: Privately Held. Founded: 2006. Specialties: Blogging, Startups, Web, Press, Blog, Web 2.0, Turkish, İnternet ...</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Yaşamartı</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/yasamarti?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Ankara, Ankara/Çankaya, TR. Get directions. 19 Mayıs Mah. 19 Mayıs Cad. No:3 ... İstanbul, İstanbul. CRYPTTECH. Data Security Software Products. Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>PrimeTek Informatics</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://ge.linkedin.com/company/primetek-informatics</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Complete UI Suite for the Modern Web. Premium components across Angular ... Software Development. Company size: 11-50 employees. Headquarters: Ankara. Type ...</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Treomind</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/treomind-make-ai-work</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>İstanbul, TR. Get directions. Ankara Kavaklıdere Mah. Bestekar Cad. No: 42/3 ... yazılım ve insan kaynağı gereksinimleri HPE Private Cloud AI ile ...</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>OktoPeople</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/oktopeople</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: Tallinn, Harju ... Yazılım Yekta Ozcan Ozozer – Digital Transformation &amp; Innovation ...</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ESEN</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/esensistem</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>... Ankara. Since the establishment, ESEN Sistem Entegrasyon has grown by leaps ... 51-200 employees. Headquarters: Çankaya, Ankara. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Goksal Aeronautics</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/g%C3%B6ksal-havacilik?trk=public_profile_experience-group-header</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ANKARA, YENIMAHALLE. Gesron Bilişim Teknoloji, A.Ş. IT Services and IT Consulting. İstanbul, Istanbul. Nevspace. Space Research and Technology. İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SSTEK SAVUNMA SANAYİ TEKNOLOJİLERİ</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/company/sstek-savunma-sanayi-teknolojileri-anonim-sirketi</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Ankara, Kahramankazan. Type: Privately Held ... Ankara, Kahramankazan 06980, TR. Get directions. Yaşam Caddesi. Beştepe ...</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Kartaca</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://lc.linkedin.com/company/kartaca?trk=products_seo_search</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>... mobil servisler, mobil uygulama, sadakat programı, bulut ... Software Development · Innovance Consultancy. IT Services and IT Consulting. Maslak, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ABIT</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/abit-consultancy/</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: ISTANBUL, İstanbul. Type: Public Company. Founded ... Junior Software Engineer jobs. 233,545 open jobs · Quality Assurance ...</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>N Kolay</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nkolay</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Esentepe, Istanbul. Type: Privately Held. Locations. Primary. Kore Şehitleri Caddesi No:8/1. Şişli. Esentepe, Istanbul 34394, TR.</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>MDP Group</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/digitalmdp</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>... web/mobile application development. MDP Group maintains its commitment to ... software.</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ZedTech</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/zedtechnet</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Yazılım, Yazılım Geliştirme, Dijital Pazarlama, Google Ads, Meta Ads, SEO, Web Tasarımı, Web Programlama, Mobil Yazılım, Mobil Tasarım, Grafik Tasarım ...</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>HepiPet</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/hepipet</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>... web sitesi üzerinden, evcil hayvan sahipleri veteriner hekimlere ücretsiz ... Istanbul, İstanbul · Jasmin Veterinary Clinic. Tutkimuspalvelut. Montréal ...</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ARETA</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/areta</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Website: https://www.areta.com.tr. External link for ARETA ; Industry: Information Technology &amp; Services ; Company size: 11-50 employees ; Headquarters: Ankara, ...</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Mono</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/company/monoyazilim</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.monodijital.com. External link for Mono ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>HappyApps</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/happydigital</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>... software technologies. Website: https://allhappyapps.com. External link for ... Gecesinde İstanbul'un eşsiz manzarasında Mobil Uygulama Sektörünün özel ...</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>GlassHouse Türkiye</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://sz.linkedin.com/company/glasshouse-turkiye?trk=products_details_guest_organization_name</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Istanbul, Sariyer. Type: Privately Held ... Ankara Patent de GlassHouse'un mutlu müşterileri arasında! Ankara Patent IT ...</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>IHS Telekom</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/company/ihstelekom</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Kıbrıs, Gazimağusa. Type: Privately Held. Founded ... Istanbul, Istanbul. Açık Holding. Holding Companies. İstanbul, Sarıyer ...</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D309"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7226,6 +7226,226 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>NGSS</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ng-software&amp;services</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, Kadıkoy. Type: Privately Held ... We're #hiring a new Senior Software Architect in Istanbul. Apply today or ...</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Modusoft</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/modusofttr</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Website: https://modusoft.com.tr. External link for Modusoft ; Industry: Software Development ; Company size: 2-10 employees ; Headquarters: Atasehir, Istanbul.</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>İş Yazılım</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/is-yazilim</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Website: http://www.isyazilim.com.tr. External link for İş Yazılım ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: Gölbaşı, Ankara.</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>DİA Yazılım A.Ş.</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diayazilim</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Çankaya, Ankara. Type: Privately Held ... DİA Yazılım - Mobil Yönetim Sistemi, Enterprise Resource Planning (ERP) Software ...</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Monad Yazılım ve Danışmanlık</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/monad-yazilim?trk=public_profile_experience-item_profile-section-card_image-click</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Monad Yazılım ve Danışmanlık. Software Development. Ankara, Ankara 3,300 followers. Sağlık yazılımında etkin proje yönetimi ve güçlü destek yaklaşımı. Follow.</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pathdevelop</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>PATH - Product and Software House IT Services and IT Consulting İstanbul, Ataşehir 37,436 followers Turn your ideas into reality and boost your business today.</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>DorukNet</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/doruknet</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>DorukNet | 4,117 followers on LinkedIn. 30 yılı aşkın süredir kapsamlı BT çözümleri ve bulut bilişimin öncüsü DorukNet. | General Overview DorukNet was founded in 1993 as a first ISP ...</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Presidency of the Republic of Türkiye Human Resources Office</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tccbiko</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Headquarters Ankara, Beştepe Type Government Agency Locations Primary Ankara, Beştepe 06560, TR Get directions Employees at Presidency of the Republic of Türkiye Human Resources Office hakan ...</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Parabol</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paraboly/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Ankara, Çankaya. Type: Privately Held ... Software Development. Çankaya, Ankara. Show more similar pages. Show fewer similar pages ...</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Key Yazılım Çözümleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/keyyazilimcom</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Key Yazılım Çözümleri A.Ş. | 8535 followers on LinkedIn. Key Yazilim has been established as a Software company in Ankara, Turkey.</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7446,6 +7446,402 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Figensoft</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://az.linkedin.com/company/figensoft</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Figensoft. Software Development. Istanbul, Türkiye 10,987 followers. The leading mobile technology company of Türkiye. Follow.</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Intime Info Yazılım Çözümleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intimeinfo/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>About us · Website: http://www.intimeinfo.com.tr/ · Industry: Software Development · Company size: 51-200 employees · Headquarters: İstanbul, Üsküdar · Type ...</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ESN Existanbul</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/esn-existanbul</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Making IT Work in ESN 💻 Continuous learning keeps our section moving forward! We recently wrapped up a great training session led by Berker Özer, ESN Türkiye’s Web Project Administrator.</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>KolayBi'</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kolaybi/</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>KolayBi' is new generation accounting and finance platform for small and medium sized businesses connects them to accountants, banks and huge range of business applications.</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>ZedPay</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/zedpaycompany</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ZedPay is a software provider, designed to power modern digital financial experiences through a single unified App.</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Schnell Global</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/schnell-global</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Schnell Global builds tech-driven companies focused on making life better for our customers. We manage a diverse portfolio of online businesses, including e-commerce, media, and software companies.</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Chainway Labs</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chainway</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Citrea took over our home city during Builders Week Istanbul! From Bitcoin++ to ETHIstanbul, Cryptist, and more - Citrea was everywhere, giving talks, leading workshops, connecting with builders ...</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Rollic</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rollic/</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Rollic is committed to producing massive scaling global titles while building a future-proof ecosystem in gaming industry.</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Signaloid</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/signaloid</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Signaloid | 10,253 followers on LinkedIn. Speed up your quantitative finance, engineering simulation, and AI/ML workloads by up to 1000x per core vs. Intel Xeon. | Signaloid provides computing ...</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Kommunity</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kommunitycom</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Kommunity is an all-in-one platform that enables organizers, brands, and groups to build, manage, and monetize their communities. From ticketing, memberships, and live streaming to content and ...</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Scrambly</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scrambly</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Scrambly | 7,246 followers on LinkedIn. User-intelligent app discovery platform fueled by rewards. Shaping the future of user acquisition. | A mobile-first discovery platform that helps users find ...</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Complead (formerly Sanction Scanner)</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/complead-ai</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>complead (formerly Sanction Scanner) is AI-native risk infrastructure for fraud and financial crime. Our Fusion engine brings onboarding, screening, monitoring, fraud prevention and investigation onto one platform. Every signal feeds one customer record and one explainable risk score, so compliance and risk teams act on real risk instead of clearing noise. What you can run on Complead ...</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Ratio Energy</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ratioenergy</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Ratio Energy Software Development Çankaya, Ankara 1,603 followers Unified Energy Intelligence View all 7 employees Report this company</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Rafineri</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rafineri</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Rafineri, online ve offline iletişim platformlarında sınırları zorlayarak pazar payı geliştirme ihtiyacındaki markalara yardımcı olan ve çalıştığı markaları popüler kültüre ...</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Biletix</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/biletix</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Biletix - Ticketmaster Türkiye | 14,737 followers on LinkedIn. We are global. We are local. | Ticketmaster, a proud division of Live Nation Entertainment, is the world's leading live event ...</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Gram Games</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gram-games</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Gram Games | 57,490 followers on LinkedIn. Gram Games is a venture-backed global mobile entertainment studio and the developer of global hits 1010!, Merged!, Six!</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Gamesporium</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/gamesporium</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Gamesporium E-Commerce Platforms Gamesporium is a PC games e-commerce platform that helps publishers and partners strengthen retail presence through thoughtful promotions, storefront visibility, and coordinated commercial activity. From launches to catalogue campaigns, we focus on creating meaningful opportunities for discoverability, conversion, and sustainable revenue growth.</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>mangolab.ai</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mangolab-ai</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>We build AI systems that run in production, not in slide decks. mangolab is an AI transformation team in Istanbul. We work in two directions at once: consulting that takes a company from ...</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D337"/>
+  <dimension ref="A1:D362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7842,6 +7842,556 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Loop Corporate</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://lv.linkedin.com/company/loop-corporate</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Loop Corporate | 31 followers on LinkedIn. Tıbbi ilaç, dermokozmetik ve diğer sağlık ürünleri ile teknolojik yazılım sektörlerinde hizmet veren Loop Corporate, alanlarında uzman ekibiyle kişilerin hayat standartlarını yükseltecek ürün ve hizmetlerin hayata geçirilmesi amacını benimsemiştir. Bu amaç ile müşteri memnuniyetini ön planda tutarak; sağlık ve kişisel ...</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>ZentrumHub</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://am.linkedin.com/company/zentrumhub/</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>ZentrumHub | 9,080 followers on LinkedIn. AI-enabled Hotel Booking Platform: Booking Engine, Supplier Connect, White Label, Agent Onboarding | ZentrumHub is a pioneering AI-powered travel technology platform transforming how OTAs, TMCs, and travel businesses connect with global hotel inventory. Founded in 2021 in Pune, India, we serve growing travel agencies worldwide. Our Mission: Become the ...</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Aksa Otomasyon</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aksaotomasyon/</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2014 yılında kurulan Aksa Otomasyon Elektrik Elektronik Sanayi ve Ticaret Limited Şirketi, endüstriyel otomasyon ve elektrik sistemlerinde uzmanlaşmış bir teknoloji şirketidir. Küresel ...</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>FINA LLC</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://ge.linkedin.com/company/fina2net</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>FINA is an international software development company with a strong focus on digital transformation for regulators, government agencies, and enterprises. Established in 2006 and rooted in SupTech innovation since 1999, FINA delivers secure, scalable, and future-ready technology solutions.</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>TURK EGITIM VAKFI</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/turk-egitim-vakfi</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>TURK EGITIM VAKFI Non-profit Organization Management İstanbul, Şişli 72,378 followers Eğitimleri, hayalleri, hikayeleri Yarıda Kalmasın.</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>İnegöl Mobilya Sanayicileri Derneği</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/inegolmobilyasanayicileridernegi/</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>İnegöl Mobilya Sanayicileri Derneği | 734 followers on LinkedIn. ABOUT US IMOS (Inegol Furniture Industrialists Association) was founded in the end of 2010 on the premises of gathering Inegol ...</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Ortana Electronic Software Contracting Inc.</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ortana</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Ortana is an R&amp;D-focused company, which designs and produces electronic and electromechanic systems. The company is specialized in Intelligent Transportation Systems and Sensor Technologies.</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Korn Ferry</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://ar.linkedin.com/company/kornferry</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Korn Ferry | 2.365.304 seguidores en LinkedIn. Korn Ferry es una empresa mundial de consultoría organizacional. Ayudamos a nuestros clientes a sincronizar la estrategia y el talento para impulsar el desempeño superior. Trabajamos con las organizaciones para diseñar sus estructuras, roles y responsabilidades.</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>UMES</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/umes</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>UMES | 17 followers on LinkedIn. Solution Partner | Universal Machine&amp;Electronic&amp;Software</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Agro TV</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/company/agro-tv</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Agro TV | 10,373 followers on LinkedIn. Tarım televizyonculuğunun "A Takımı" ile sizlerleyiz ! | Agro TV Turkey tarımda bilginin ve medyanın gücünü, sektörün ve çiftçilerin kalkınması için kullanarak gelişen bir medya kuruluşudur.</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ALBARS</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/albars</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>ALBARS | 482 followers on LinkedIn. ALBARS - Microsoft Gold Partner, developing the most innovative IT solutions that ensure your company growth. | Our goal is the development and the implementation of the most innovative and cutting-edge IT infrastructure solutions. We believe that IT solutions we provide, may significantly enhance the productivity and efficiency of any entity’s IT ...</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Fortune Mine Games</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://ps.linkedin.com/company/fortunemine-games</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>About us Fortune Mine Games is a mobile gaming startup. Focused on social &amp; casual mobile games in newly emerging sub-genres and aims to develop genre-definer titles. Headquartered in Istanbul; an emerging mobile gaming hub. Website https://fortunemine.com External link for Fortune Mine Games Industry Mobile Gaming Apps Company size 11-50 employees Headquarters Istanbul, Kadikoy Type Privately ...</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Complead (formerly Sanction Scanner)</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://ga.linkedin.com/company/complead-ai/</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>We are a G2 AML Leader and a Deloitte Technology Fast 500 EMEA company, with offices in Istanbul, London and New York. Learn more at complead.ai Website https://complead.ai/ External link for Complead (formerly Sanction Scanner) Industry IT Services and IT Consulting Company size 51-200 employees Headquarters London Type Privately Held Founded ...</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Thomas Cook</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://fx.linkedin.com/company/thomascooktourism</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Thomas Cook | 139 768 abonnés sur LinkedIn. In 1841, Thomas Cook became a pioneer of the travel industry. He recognised that by buying a full carriage of seats from a train operator he could both fill the carriage and save the passengers money on their ticket. From those humble beginnings, an entire global industry of package travel was born.</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Buddi</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/company/buddi</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Buddi is a trusted and reputable supplier of advanced, high-quality products and services for the Criminal Justice and remote care monitoring sectors. Buddi’s solutions are trusted by corrections agencies and law enforcement globally for electronic monitoring and offender management. Criminal Justice: Our solution consists of a proprietary web-based monitoring software platform (Eagle) with ...</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Complead (formerly Sanction Scanner)</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/company/complead-ai/</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>We are a G2 AML Leader and a Deloitte Technology Fast 500 EMEA company, with offices in Istanbul, London and New York. Learn more at complead.ai Website https://complead.ai/ External link for Complead (formerly Sanction Scanner) Industry IT Services and IT Consulting Company size 51-200 employees Headquarters London Type Privately Held Founded ...</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ZentrumHub</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://fk.linkedin.com/company/zentrumhub/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>ZentrumHub | 9,090 followers on LinkedIn. AI-enabled Hotel Booking Platform: Booking Engine, Supplier Connect, White Label, Agent Onboarding | ZentrumHub is a pioneering AI-powered travel technology platform transforming how OTAs, TMCs, and travel businesses connect with global hotel inventory. Founded in 2021 in Pune, India, we serve growing travel agencies worldwide. Our Mission: Become the ...</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ITEA 4</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://mt.linkedin.com/company/itea4</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>ITEA 4 | 3,721 followers on LinkedIn. ITEA, the Eureka Cluster for software and systems innovation: your agenda, your innovation - achieved together | ITEA, the Eureka Cluster for software and systems innovation, is the place where you turn your innovation ideas quickly into reality, in areas that matter to you, by collaborating in funded RD&amp;I projects that create real impact. ITEA brings ...</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>HRPeak</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://to.linkedin.com/company/hrpeak/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>HRPeak | 10,037 followers on LinkedIn. HRPeak | your digital HR solutions partner | HRPeak is an online assessment platform that produces digital HR solutions. A pioneer in the industry, HRPeak combines innovative ideas with expertise to present a unique digital platform that brings together various assessment tools. HRPeak has quickly established itself nationally as a game changer in the ...</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>UPTION</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/uptionint</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Senior Software Developer | .NET |… Click here to view Ahmet K.'s profile ... İstanbul, Şişli · Aktif Bank. Investment Banking. Esentepe, İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>JFORCE</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/jforce?trk=public_profile_topcard-current-company</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>We're #hiring a new Java Yazılım Mühendisi in Istanbul. Apply today or share ... Web Developer jobs · Software Test Engineer jobs · System Analyst jobs ...</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Caretta</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/caretta</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.caretta.net/. External link for Caretta ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: istanbul.</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>HTM Design Inc.</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/htm-design-inc</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Locations. Primary. İvedik Caddesi. Teknopark Ankara İvedikOSB Mah. 2224. Cad ... Software Engineer jobs. 300,699 open jobs · Business Application Manager ...</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>aqtivite</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aqtivite</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>... mobil uygulama olarak hayata geçtik. Aqtivite ... Software Development. Pamukkale, Denizli 77 ... Antalya, Antalya · Kami: Create. Read. Socialize ...</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>AET Electronics</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aet-electronics/</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Saray, Ankara. Type: Privately Held. Founded: 2019 ... Software Development · Aselsan. Defense and Space Manufacturing. Mehmet ...</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D362"/>
+  <dimension ref="A1:D379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8392,6 +8392,380 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Atacom Information Systems</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/atacom-information-systems</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Kayışdağı Cad. Sevinç Sok. No:5 Pasific Plaza A Blok Kat:4. Ataşehir, İstanbul 34750, TR ... Tarvina Yazılım Teknoloji. Software Development. SecHard. Computer ...</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>JourneyApp</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/journeyapp</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://www.journeyapp.com/tr/ana-sayfa. External link for JourneyApp ; Industry: Software Development ; Company size: 11-50 employees.</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Arvasyon Yazılım Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arvasyon</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>External link for Arvasyon Yazılım Teknolojileri. Industry: Mobile Gaming Apps. Company size: 2-10 employees. Headquarters: İstanbul, Esenyurt. Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>WAGNIFY Bilgi Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wagnify</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>We're #hiring a new Senior Sales Manager in Istanbul, Istanbul. Apply today ... Fortune 500 şirketlerinin %62'si hâlâ 20 yıldan eski yazılım kullanıyor.</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Sepet Takip</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sepet-takip</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://sepettakip.com/. External link for Sepet Takip ; Industry: Software Development ; Company size: 11-50 employees ; Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>SorsX</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sorsx</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>... software, Recruiting software, and interviewing software. Locations. Primary ... Ankara'da insan kaynaklarının geleceğini konuşmak, gerçek sorunları ...</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>MIKRODEV AUTOMATION</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/mikrodev</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>... software products used in automation, telemetry, and SCADA systems, offering them ... Kocaeli, Kocaeli · Armoli. Appliances, Electrical, and Electronics ...</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>SmartEquip</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://na.linkedin.com/company/smartequip</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>SmartEquip | 5,076 followers on LinkedIn. Be Ready. | SmartEquip is the leading technology standard for equipment lifecycle management, service, and procurement support for the global construction industry. The platform provides a seamless brand-enhancing experience for fleet owners, manufacturers, and distributors of complex equipment. SmartEquip enhances ROI for all Network participants by ...</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Kinemetrics, Inc.</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/kinemetrics</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Kinemetrics, Inc. | 2,760 followers on LinkedIn. Advancement through Innovation | Since 1969 Kinemetrics and its subsidiaries continue to lead the global market in designing technologies, products, and solutions for monitoring earthquakes and their effects on people and structures. We are located in Pasadena, California, also known as ͞Earthquake Country. Today, we continue to lead the ...</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Utest Material Testing Equipment</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://mw.linkedin.com/company/utestgroup</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Utest manufacturing all equipment software and hardware within its own structure, including CNC machining, welding, painting, and assembling. UTEST is the first choice in the sector. All Utest products are designed, analyzed and manufactured by using the latest technology.</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>AUDİS Arşiv Uygulamaları ve Doküman İşleme Sistemleri Ltd ...</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://dj.linkedin.com/company/audis-arsiv-uygulamalari-ve-dokuman-isleme-sistemleri-ltd-sti</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>AUDİS Arşiv Uygulamaları ve Doküman İşleme Sistemleri Ltd. Şti. | 814 followers on LinkedIn. AUDİS Arşiv Uygulamaları, 2017 yılından bu yana dijital dönüşüm, doküman yönetimi ve arşiv teknolojileri alanında faaliyet göstermektedir. Kurumların kağıtsız ve süreç odaklı çalışma modeline geçişini sağlama misyonuyla kurulan AUDİS; sektör deneyimini, kendi ...</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Albert Health</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://tc.linkedin.com/company/albert-health</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Albert Health Hospitals and Health Care İstanbul, Ataşehir 8,772 followers Albert is an evidence-based multi-chronic disease management platform that leverages AI.</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Valora Consultores</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://sl.linkedin.com/company/valora-consultores</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>About us VALORA is a consulting company who focus its activity towards a new professional innovative and thrilling challenge. Since 1995 a team of professional workers works in order to help public and private organizations to approach the new challenges of global sustainability, helping them to look over and reconfigure their business models, combining innovation, creativity and technology ...</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Poki</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://wf.linkedin.com/company/poki?trk=organization-update_share-update_actor-image</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Poki | 8,226 followers on LinkedIn. Reaching 100+ million players every month, we&amp;#39;re creating the ultimate free web games playground to Let the World Play! | At Poki, play is how we learn. That&amp;#39;s why we’re on a mission to create the ultimate free web games playground. With tons of games for all ages and interests, we’re bringing fun to 100+ million players every month.</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Tekno Mühendislik ve Danışmanlık San. Tic. Ltd. Şti.</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/teknomuhendislik</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, Silivri. Type: Privately Held. Locations ... Browse jobs. Electrical Specialist jobs. 47,476 open jobs · Software Test ...</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Data Sistem A.S.</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/data-sistem-a-s-?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Kavacık, Istanbul 34810, TR. Get directions. Mustafa Kemal Mah. 2118 Cd. 06510, Ankara ... Software Development. Limeira, SP. Data Market. Information Technology ...</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>AdCubes</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adcubes</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Besiktas, Istanbul. Type: Privately Held. Founded: 2025 ... Istanbul, Istanbul · Codeway. Software Development. Barcelona, ...</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D379"/>
+  <dimension ref="A1:D396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8766,6 +8766,380 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Platform97</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/platform97</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Kadikoy, Istanbul. Type: Privately Held. Locations. Primary. Bağdat Caddesi. Kadikoy, ...</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>AILab</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ailabtrcom</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>AILab şirketinde Yazılım Mühendisi |… See all employees. Updates. View ... 12 Şubat 2026 tarihinde Ankara Sanayi Odası Ankara Sanayi Odası Zafer ...</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ESEN</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://si.linkedin.com/company/esensistem</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>... Ankara. Since the establishment, ESEN Sistem Entegrasyon has grown by leaps and bounds. We are proud to announce that European Software Institute (TECNALIA) ...</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Miuul</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/miuul</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Malmö. Type: Privately Held. Founded ... Similar pages. Veri Bilimi Okulu. Information Technology &amp; Services. Istanbul, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Wowoo</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/wowoostudios</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>We're #hiring a new Senior Web Application Developer in Istanbul. Apply ... Software Development. Barcelona, Catalonia · HubX. Software Development · Lucida ...</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Anatolya Technology</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/anatolyatechnology</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Our expertise spans web and mobile application development, digital transformation projects, AI-powered analytics systems, and innovative software solutions, ...</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>TÜBİTAK BİLGEM KAMU SERTİFİKASYON MERKEZİ</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/kamusm</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Gebze, Kocaeli. Type: Government Agency. Founded ... Coordinator &amp; Head of Software… See all employees. Similar pages. TÜBİTAK ...</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ShipEntegra</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/shipentegra</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>is a web ... software in its own facility. Since from 2017 we have tripled our employee number. Four in US and ten in TR such as İstanbul (2), Antalya, Ankara ...</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>DataHome® Data Center</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/datahometr</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>51-200 employees. Type: Privately Held. Employees at ... FinOps | Financial &amp; Operational Intelligence. Business Intelligence Platforms. Antalya, Antalya.</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>3E</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://mk.linkedin.com/company/3eeos</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>... Software Engineering, Day Vision, Riflescope, Customer Service, STEM, Sales and Marketing, Service &amp; ILS, and Spotting Scope. Locations. Primary. Ankara, 06935, ...</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Nethouse</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://cm.linkedin.com/company/nethousetr?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Sarıyer, İstanbul. Type: Privately Held. Founded ... Software Development. Istanbul, Sarıyer · Trendyol Group. Technology ...</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Komuneo</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/komuneo?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>... yazılım konusunda çözüm ortaklığı sunuyor. Komuneo olarak yıllar içinde ... İstanbul, Istanbul · Rayelin Hotels. Hotelli- ja ravintola-ala. Fatih, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Potensas</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/potensas</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: Maslak, İstanbul ... PixelByte. Software Development. Çankaya, Ankara. Show more similar pages</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>TELIBRAHMA SOFTWARE SERVICES LLP</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/telibrahma-software-services-llp</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>External link for TELIBRAHMA SOFTWARE SERVICES LLP. Industry: Information Technology &amp; Services. Company size: 11-50 employees. Headquarters: Bangalore, ...</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ShopiVerse</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/shopiverseuk</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>... software company that offers artificial intelligence-powered, cross-border e ... 11-50 employees. Headquarters: United Kingdom, Maidenhead, Snf C385 ...</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Emi Grup Information Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/company/emigrup</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>... software ... İstanbul, Marmara 34662, TR. Get directions. İşçi Blokları Mahallesi Muhsin Yazıcıoğlu Caddesi. La Vida City İş Merkezi No:45 A / 4. Cankaya, Ankara, ...</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Evant Teknoloji</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/evant-teknoloji%CC%87</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Evant Teknoloji | Veeam Software . ... Similar pages. EFA Bilgi Sistemleri. IT Services and IT Consulting. Kahramanmaraş-Gaziantep-İstanbul-Tekirdağ-Adana, Merkez ...</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D396"/>
+  <dimension ref="A1:D426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9140,6 +9140,666 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Validos Biomedical R&amp;D</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/validos-biomedical/</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Ankara. Type: Privately Held. Founded: 2020 ... Take Off İstanbul etkinliği benim için beklenmedik güzel tanışmalara ve bağlantılara ...</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Krizma Software Co</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/krizmasoftware?trk=public_profile_topcard-current-company</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>... Ankara. He started his business life by targeting National Software Projects by the ... 11-50 employees. Headquarters: Beytepe ÇANKAYA, ANKARA. Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>KUVARS</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/kuvarstech/</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Metaverse Software - Metaverse Yazılım. Ohjelmistokehitys. Ankara, Cankaya · Peak. Tietokonepelit. Istanbul, TR · Huma. Verkko-opetuksen tarjoajat · GAGA ...</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ATEL Technology and Defense</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/atel-teknoloji-ve-savunma-sanayi</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>ATEL Technology and Defense, established in Ankara, Turkey, in 1997, is a ... SADIK YILDIRIM. Senior Software Developer | ASP.NET MVC… See all employees ...</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>SORWE</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/sorwe-bilgi-ve-mobil-teknolojileri-ltd-ti</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Website: https://www.sorwe.com. External link for SORWE ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: London &amp; Istanbul, . ; Type ...</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Pisano</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/pisano</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Software Development. London, England 8,534 followers. All-in-One Experience ... İstanbul, Turkey 34467, TR. Get directions. Business Village, Port Saeed.</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>AgrInnovate EDIH</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/agrinnovate-edih</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>... Mersin Ticaret ve Sanayi Odası / Mersin Chamber of Commerce &amp; Industry YASAD Yazılım ... AgrInnovate EDIH web sitesi yayında! Tarım ve gıda sektöründe ...</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>ARMELSAN</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://az.linkedin.com/company/armelsan-savunma-teknolojileri?trk=public_profile_experience-item_profile-section-card_image-click</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>... Software, Hardware and System Development, R&amp;D, System Engineering, Depot ... İstanbul Teknik Üniversitesi Havacılık ve Uzay Araştırmaları Merkezi Müdürü Prof.</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Robosys Mekatronik Sistemleri Sanayi ve Ticaret Limited ...</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/robosys-mekatronik-sistemleri-sanayi-ve-ticaret-limited-%C5%9Firketi</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Ankara, Yenimahalle. Type: Privately Held. Founded ... Browse jobs. C Developer jobs. 35,747 open jobs · Embedded Software Engineer ...</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Vertigo Games</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/vertigogames</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters ... Besiktas, Istanbul · Codeway. Software Development. Barcelona, Catalonia · Agave Games. Mobile Gaming Apps. Şişli, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>KG&amp;BG Business Group</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kg-bg-business-group</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>... Yazılım ve teknoloji odaklı şirketlerin rekabet avantajı kazanarak pazarda ... 11-50 employees. Type: Partnership. Founded: 2025. Employees at KG&amp;BG ...</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>YAKATECHPRO BİLGİ SİSTEMLERİ LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/upextech</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Pendik, İstanbul. Type: Partnership. Founded: 2021 ... Mobil uygulama, UpexTag donanımı ve admin panelini tek bir sistemde ...</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Acıbadem Technology</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://tt.linkedin.com/company/ac%C4%B1badem-technology</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>In 2015, Acıbadem Technology provided its services through Software and Infrastructure in Acıbadem Healthcare Group, for; 3.500 doctors and 4.000 nurses, 2750 ...</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Pangea Danışmanlık A.Ş.</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/pangea-consultancy-and-trade-co</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Sisli, Istanbul. Type: Privately Held ... We're #hiring a new Project Finance Analyst / Credit Analyst in Istanbul, Istanbul.</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>BiSU</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tek-tu%C5%9F'la-bisu/</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Istanbul, Istanbul. Type: Partnership. Founded: 2015. Locations. Primary. Sair Nefi Sokak 23. Istanbul, Istanbul 34710, TR. Get ...</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Armeva</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://pk.linkedin.com/company/armeva?trk=public_profile_experience-item_profile-section-card_image-click</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>About us ; Industry: Marketing Services ; Company size: 11-50 employees ; Headquarters: Ankara ; Type: Partnership ...</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Radore</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/radore</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>... Web Hosting, Managed Services) to its customers with 100% physical security ... Locations. Primary. Metrocity. Levent. Istanbul, 34340, TR. Get directions ...</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>WebInStats</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/webinstats</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>WebInStats. Software Development. Istanbul, Istanbul 481 followers. Personalization,OmniChannel Marketing,OnSite Marketing,InApp Marketing,Web Push, ...</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Intelivus AI</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intelivus?trk=public_post_main-feed-card-text</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul. Type: Privately Held. Locations. Primary ... yazılım birimleridir. Bu teknoloji, işletmelere yalnızca süreç ...</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>NOZZLE</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://ls.linkedin.com/company/nozzle-ship-management-software?trk=products_seo_search</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Ataşehir. Type: Privately Held. Founded ... NOZZLE - Ship Management Software, Istanbul, Istanbul, Türkiye · 4 · Like ...</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Demir Denetim Mali Müşavirlik A.Ş</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/demir-denetim-mali-m%C3%BC%C5%9Favirlik</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>... yazılım, gıda ve perakende sektörlerindeki ... Samankaltaisia sivuja. Oz Denetim ve Kontrol Danışmanlık. Yrityskonsultointi ja -palvelut. İstanbul, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>LA2 DYNAMICS Mühendislik A.Ş</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/la2-dynamics?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>LA2 DYNAMICS, which has offices in Ankara Bilkent CYBERPARK and Istanbul ARI Teknokent, carries out R&amp;D activities in the field of Robotics. Website: https ...</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Ambeent</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ambeent</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>İstanbul, TR. Get directions. Employees at Ambeent. Click here to view Mustafa ... Data Science, Software Development… Click here to view Sheldon ...</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>MonoPayments</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/monopayments</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: London. Type: Privately Held. Founded: 2020 ... Software Developer. Click here to view Fatih Ermis' profile. Fatih Ermis.</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>WittyCar</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/wittycar</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Kadikoy, Istanbul. Type: Partnership ... Similar pages. Kartek Software | Software &amp; Mobile Application Development Company.</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>FineSci Technology Inc.</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/finesci/</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Toimiala: Ohjelmistokehitys. Yrityksen koko: 2-10 employees. Päätoimipaikka: Çifte Havuzlar, Istanbul.</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Volt Lines</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/voltlines</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>İşveren Web Uygulaması Müşteriler tek bir web uygulaması aracılığıyla tüm ... Istanbul Metropolitan Municipality (İBB) and Metro Istanbul. What ...</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>İnno Teknoloji Elektronik San. ve Tic. Ltd. Şti.</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/inno-teknoloji?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>... yazılım ve donanımlar geliştirmek üzere AR-GE şirketi olarak 2012 yılında ... Esenşehir Mh. Natoyolu Cd. No:221 Kat:2. İstanbul, Ümraniye 34776, TR. Get ...</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>B2Metric</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/b2metric</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Dover ... İstanbul, Turkey 34906, TR. Get directions. Employees at B2Metric. Click here to ...</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>NovaForge</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/novaforge</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Dover, Delaware. Type: Privately Held. Founded ... İstanbul, İstanbul · HiRi.ai. Software Development · Infodeal Business Solutions.</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D426"/>
+  <dimension ref="A1:D428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9800,6 +9800,50 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>OPTiiM</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/optiim</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>OPTiiM is a software and services company based in Istanbul, London, Dublin and Toronto. ... 51-200 employees. Headquarters: Istanbul, Sisli. Type: Partnership.</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>CodiaSoft Software Agency</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/codiasoft</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2-10 employees. Type: Privately Held. Founded: 2021. Employees at CodiaSoft ... Click here to view Samsun Web Tasarım's profile. Samsun Web Tasarım. CodiaSoft ...</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D428"/>
+  <dimension ref="A1:D429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9844,6 +9844,28 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Genex Yazılım A.Ş.</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/genex-yaz%C4%B1l%C4%B1m-a.%C5%9F.</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Genex Yazılım A.Ş. | 1888 followers on LinkedIn. Genex Yazılım A.Ş, Mart 1994 yılından itibaren İstanbul'da faaliyet gösteren bir yazılım ... 11-50 employees.</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D429"/>
+  <dimension ref="A1:D442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9866,6 +9866,292 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>CODEBASE Ar</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/codebase-arge</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>CODEBASE is an agile software company that develops enterprise-scale web and mobile software products and solutions ... 11-50 employees. Headquarters ...</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Byterise</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/byteriseco/</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul. Type: Privately Held. Locations. Primary ... React Native Developer. Click here to view Gorkem Colakogullari's ...</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Arute Solutions</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arutesolutions</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held ... Istanbul konumunda yeni bir Software Engineer için işe alım yapıyoruz #hiring.</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Bitwise Yazılım</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bitwise-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Kocaeli. Type: Privately Held. Founded: 2020. Locations. Primary. Kocaeli, TR. Get directions. Employees at Bitwise Yazılım. Click ...</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>AppTech Systems LLC</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/apptech-systems</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Our core expertise encompasses bespoke software, innovative web and mobile ... 11-50 employees. Headquarters: Başakşehir , İstanbul. Type: Public Company.</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>COP31 Türkiye</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/turkiyecop31</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Accredited media personnel and delegation media teams are kindly requested to review the guidelines, submit filming requests at least 5 days in advance using the required subject line, and ...</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>ReOrbit</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reorbit</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>ReOrbit | 25,241 followers on LinkedIn. Founded in 2019 and headquartered in Helsinki, Finland, ReOrbit is a fast-growing European space technology company that manufactures sovereign satellites ...</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Neurotechnology</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neurotechnology</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Neurotechnology is a developer of high-precision algorithms and software based on deep neural networks and other AI-related technologies. The company was launched in 1990 in Vilnius, Lithuania ...</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Manus Software</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/manussoftware/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: ANKARA, -. Type: Privately Held. Founded: 2008 ... See you at the Manus Software booth at MAKTEK Istanbul. Manus Yazılım ...</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Your Software Supplier</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/yoursoftwaresupplier</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Privately Held. Founded: 2019. Specialties: Software Marketplace, Software Ecosystem, Custom Software Development, Web ... İstanbul, İstanbul 34770, TR. Get ...</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Uplico</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/uplico</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>... Software Engineering olarak Türkiye'nin en büyük teknoloji ekiplerinden ... Software Development. İstanbul, İstanbul · Vitsupp by Marin. Wellness and ...</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Mono</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/monoyazilim</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Website: http://www.monodijital.com. External link for Mono ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: İstanbul, Beşiktaş.</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Runibex</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/runibex</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>We build, run, and modernise software products on cloud, for ourselves first and for the enterprises we serve. Founded in 1988 with offices in Istanbul and ...</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D442"/>
+  <dimension ref="A1:D457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10152,6 +10152,336 @@
         </is>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Up and Running Software, Inc.</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/up-and-running-software-inc.</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>External link for Up and Running Software, Inc. Industry: Technology, Information and Internet. Company size: 51-200 employees ... Web Services (AWS), Systems, ...</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Ventura Yazilim</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/venturayazilim</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>İstanbul, Maslak · Netcad. Software Development. Çankaya, Ankara · Curiosity Technology. Software Development. İstanbul, Istanbul · EgeSoft | Makina Yazılım.</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Baytek Software Development Corp.</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/baytekdev</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Type: Privately Held. Founded: 1985. Specialties: Mobile (Native, Cross), Web (React, Angular etc.) Desktop ...</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>PrimeIT Bilişim A.Ş</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/primeit-a-%C5%9F</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>... Yazılım geliştirme projeleri üretir ve danışmanlık hizmeti sunar. PrimeIT ... 51-200 employees. Headquarters: İstanbul, Ataşehir. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Reload</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/reloadapp/</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Mobile Computing Software Products. Company size: 2-10 employees. Headquarters: Antalya. Type: Privately Held. Founded: 2022. Specialties: Mobile App, Mobile ...</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Rising Digital</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/risingdigital</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Kagithane, Istanbul. Type: Partnership ... Software Engineer | Web Scraping •… Click here to view İrem Köse's profile ...</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Miletos Inc.</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/miletos</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>... Software (FLOSS), Optical Character Recognition (OCR), Image Processing ... İstanbul, İstanbul/Beyoğlu · Etcbase Yazılım ve Bilişim Teknolojileri A.Ş ...</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Rnv.ai</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rnv-analytics/</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Software Development. İstanbul, Istanbul 5,345 followers. RNV Analytics is an ... Antalya, Antalya. Trendyol Group. Technology, Information and Internet.</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>capoom</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/capoom</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>It enables developers to generate customized 3D assets without the need for any 3D modeling software expertise. ... Istanbul in Istanbul. Apply today or share ...</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Kreios Space</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kreiosspace</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Kreios Space Aviation and Aerospace Component Manufacturing Vigo, Pontevedra 9,710 followers Kreios develops Very Low Earth Orbit satellites that operate at 200 km from Earth. Closer than ever.</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Hexaly</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hexaly</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Hexaly | 21,664 followers on LinkedIn. The next-generation MIP solver | Go beyond traditional MIP with combinatorial, nonlinear, and simulation-based optimization. Hexaly enables developers to ...</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Huma</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/huma-finance</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Huma Software Development Huma accelerates global payments with instant access to liquidity anywhere, anytime.</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Hemosoft IT &amp; Training Services Inc.</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hemosoft-it-&amp;-training-inc-</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>... Ankara, Turkey, initially focusing on medical software development with ... web and PC-based applications.</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Inventra</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/inventra-ai</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>... software development, cloud integration, and digital transformation consulting. ... Teknopark Ankara, Yenimahalle-Ankara, Ankara · BlueSense. Business Consulting ...</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>DECE Software</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/decesoftware</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>We're excited to announce that DECE Software will be participating in IDC Security Summit Türkiye 2026! Join us on October 13 in Istanbul, where we'll be ...</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D457"/>
+  <dimension ref="A1:D484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10482,6 +10482,600 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>kloia</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kloia</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>kloia and Amazon Web Services (AWS) hosted Cloud and AI Excellence for ... Istanbul, TR. Parny. Software Development. Oxtractor. Software Development.</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Aksungur Software</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aksungur-software</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Aksungur Software | 57 followers on LinkedIn. Design &amp; Development | Aksungur Software web ... Antalya, Antalya. Primo Family Club. Retail Apparel and ...</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Kle Information Technologies</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kle-information-technologies</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Kle Information Technologies | 766 followers on LinkedIn. Kle Information Technologies is Software Outsourcing &amp; Development service provider offering ...</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Earsis Technologies Ltd. Şti.</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/earsis-ltd.-%C5%9Fti.</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Çankaya, Ankara. Type: Privately Held. Founded: 2016 ... We're #hiring a new Senior Embedded Software Engineer in Ankara, Ankara.</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Bizitek</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bizitek</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Software Development. Maslak, Istanbul 3,208 followers. Follow · Report this company; Close menu. View all 17 employees. About us. Bizitek was founded in 2000 ...</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Intellity Artificial Intelligence Solutions</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intellity-ai-solutions/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Küçükçekmece. Type: Privately Held ... software. The Lena Core Engine is used in enterprise solutions developed by ...</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Telenity</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/telenity</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Istanbul, Türkiye. Type: Privately Held. Founded: 2000. Specialties: Software, Digital ...</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>SESTEK</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sestek</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Website: http://www.sestek.com. External link for SESTEK ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: Sarıyer, İstanbul ; Type ...</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>MobileAction</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mobile-action</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Ankara, TR. Get directions. Berlin, DE. Get directions. Istanbul, TR. Get ... Hazal Orta'nın haberinin tamamı web sitemizde. https://lnkd.in/dwz5G7A9 ...</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Talentics</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/talenticsapp</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Talentics is an innovative recruiting software and an HR tool that ... Software Development. Company size: 2-10 employees. Headquarters: Istanbul. Type ...</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>EXEDRA HRTech Company</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/exedra-hrtech-company</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Website: http://www.exedra.com.tr. External link for EXEDRA HRTech Company. Industry: Software Development. Company size: 11-50 employees.</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Piple</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pipleco</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: San Francisco, CA. Type: Privately Held ... Software Engineer | Backend, Web &amp;… Click here to view nakisa bavarsad's ...</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>4ARC Yazılım Teknolojileri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/4arctech</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Avcılar, İstanbul. Type: Privately Held. Founded: 2018. Specialties: Bankacılık Yazılım Geliştirme, Mobil Bankacılık ...</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Marka Works</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/markaworks</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: London, England. Type: Privately Held. Founded: 2015. Specialties: Branding, Print Design, Art Direction, Packaging Design, Web ...</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>TechNarts</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://ls.linkedin.com/company/technarts/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.technarts.com. External link for TechNarts-Nart Bilişim ; Industry: Software Development ; Company size: 51-200 employees.</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>EVAM</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/evamtech</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>EVAM. Software Development. Istanbul, Istanbul 28,264 followers. A leading ... 51-200 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>SchemaPlus</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/schemaplus-inc</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Similar pages. Uppercase Brands. Advertising Services. New York, NY · F4e. Software Development · Softtech. IT Services and IT Consulting. Istanbul, Turkey ...</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Magicorn</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/magicorn</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>... İstanbul'da ama bu bize tam olarak hangi servislerde, ne avantaj sağlayacak?" Geçtiğimiz günlerde Magicorn olarak katıldığımız Amazon Web Services (AWS) ...</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Aequilibrium</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/aequilibrium-software</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>... Web Design, User Experience Design, Usability Testing, Codeless Prototyping, Web Development, Digital Roadmaps, Lean Canvas, Software ... Istanbul exploring ...</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Volosoft</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://sz.linkedin.com/company/volosoft?trk=products_seo_search</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Website: https://volosoft.com. External link for Volosoft ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: Istanbul, Bakırköy ; Type ...</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>MDP Group</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/digitalmdp?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>... web/mobile application development. MDP Group maintains its commitment to ... Software Development. Kadikoy, Istanbul · Nagarro + MBIS. IT Services and IT ...</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Sistek</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sistek</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Website: http://www.sistek.com.tr. External link for Sistek ; Industry: IT Services and IT Consulting ; Company size: 11-50 employees ; Headquarters: İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getverify</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: New York, NY ... Web Designer jobs · Commercial Director jobs · User Experience Specialist ...</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>ANT SOFT</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/antsoftech</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Austin, Texas. Type: Public Company. Founded: 2017. Specialties: Cloud Solutions, CRM Implementation, Custom Software ... İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Telenity</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/telenity</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Telenity. Software Development. Istanbul, Türkiye 23,777 followers. Harness the true power of your network. Follow.</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>ATEZ</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/atezsoftware</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>ATEZ Software Technologies is a forward‑looking technology company ... İstanbul, Istanbul. Juuli. Financial Services. Show more similar pages. Show ...</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>DeSL</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/desl</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Cardiff. Type: Privately Held. Founded: 2002. Specialties: PLM, ERP, CRM and E-Commerce ...</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D484"/>
+  <dimension ref="A1:D503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11076,6 +11076,424 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Efectura</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/efectura</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Istanbul. Type: Partnership. Founded: 2016. Locations. Primary. Istanbul. Istanbul, Istanbul 34000, TR. Get directions.</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>ARGEDOR Information Technologies</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/argedor-bili-im-teknolojileri-ltd-</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>11-50 employees ... Hakan Yavuzyigit · See all employees. Similar pages. MindMons Technologies. IT Services and IT Consulting. Ankara, Ankara/Çankaya ...</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Fimple</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/fimpleos</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: London, United Kingdom. Type: Public Company ... Teknopark İstanbul, İstanbul · Dünya Katılım. Banking · İktisat Katılım. Banking ...</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Odito App</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oditoapp/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Employees at Odito App ; Mustafa Yücedağ. Founding Partner &amp; CIO at Nuevo Yazılım… ; Ali Haydar Durmuş. Senior Fullstack Software Developer ; Pelin Turker. Sales ...</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>CPM YAZILIM</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cpm_2/</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.cpm.com.tr. External link for CPM YAZILIM ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: İstanbul.</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Beakwise</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beakwise</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>... Software &amp; Core Systems Strategic Advisory &amp; Bespoke Engineering ... We're #hiring a new Senior BI &amp; Data Analyst in Istanbul, Istanbul. Apply ...</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Agave Games</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/agavegames?trk=public_profile_experience-item_profile-section-card_subtitle-click</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Website: https://www.agavegames.com/. External link for Agave Games ; Industry: Mobile Gaming Apps ; Company size: 51-200 employees ; Headquarters: Şişli, Istanbul.</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>BackupSec Software</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/backupsec</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Chevening, England. Type: Privately Held ... Tanbu. Software Development. Atasehir, Istanbul. Show more similar pages. Show ...</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Digiform Yazılım</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/digiform-yaz%C4%B1l%C4%B1m-a.%C5%9F.</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>... software and hardware solutions for almost any platform, including ... İstanbul, istanbul · Papirus AI. Software Development · İSTANBUL YAZILIM. Software ...</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Axisbits</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/axisbits</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>The software studio for businesses that want to build, automate and scale. ... Web Development, Web Design, QA, E-commerce, SaaS, CRM, Startups, ERP, and ...</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Random Bilişim Yazılım Hizmetleri</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/random-bili%C5%9Fim</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul. Type: Public Company. Founded: 2016. Specialties: php, web ... Similar pages. Dokuzsoft Teknoloji Ltd Şti. Software ...</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Renova Consulting</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/renovaconsulting</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>... software segment. We become your partner with our team specialized in all ... 51-200 employees. Headquarters: Istanbul, Üsküdar. Type: Partnership. Founded ...</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Nodelabs Software</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/nodelabs-software</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>From mobile software development and web applications to digital marketing ... 11-50 employees. Headquarters: London, England. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Kavaken</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/kavaken</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>... Istanbul, Turkiye its offerings deliver value to asset owners, lenders ... Supervisory Control and Data Acquisition (SCADA) Software. The Kavaken ...</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Medianova</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://mw.linkedin.com/company/medianovacdn?trk=products_seo_search</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>... Web Application Firewall, and DDoS Protection. With its footprint of 50 ... Locations. Primary. Sehit Ahmet Sokak. Mecidiyekoy Is Merkezi, Kat 15. Istanbul, ...</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>MetaForm Inc.</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/company/metaform-bilisim-ltd</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Monad Yazılım ve Danışmanlık. Software Development. Ankara, Ankara. S4E. Computer and Network Security. Show more similar pages. Show fewer similar pages.</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>TRAICK</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/traick</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Software Development. Abrakadabra Games. Computer Games. istanbul, Istanbul. Softtech. IT Services and IT Consulting. Istanbul, Turkey. MediSense AI. Software ...</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>flexigo</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/flexigo</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Los Angeles ... Istanbul, İstanbul. TalenTown İnsan Kaynakları - İşe Alım Ajansı. Human ...</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Holyum Yazılım Donanım Mühendislik Danışmanlık San. ...</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/holyum</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Holyum Yazılım Donanım Mühendislik Danışmanlık San. Tic. LTD. ŞTİ. Software Development. Yenimahalle, Ankara 96 followers. Bilgi ve teknoloji çağında akıllı ve ...</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11494,6 +11494,578 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>TR7</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/tr7-asp</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>... web traffic, protects sensitive data, and ensure the security ... Istanbul, Istanbul · Securify Identity. Computer and Network Security. Ankara ...</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Appwise OÜ</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/appwise-ou</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.appwise.ee. External link for Appwise OÜ ; Industry: Software Development ; Company size: 2-10 employees ; Headquarters: Tallinn, ...</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Narkom Communication and Software Technologies</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/narkom-communication-and-software-technologies</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Şişli, Istanbul. Type: Privately Held. Founded: 2017. Specialties: Network Technologies, Data Center, Software Developments ...</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Countly</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/countly</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: London ... Web Analytics, IoT Analytics, Desktop Analytics, Customer Experience, GDPR ...</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Etsetra</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/etsetra</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>... web sitesi oluşturun. Kod yok. Tasarımcı yok. Ajans yok. Sadece işinizi anlatın. Gerisini AI halleder. ✔️ Mobil ... Software Development. London, England ...</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Yacoda</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/yacoda</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>SCIENTIFIC SOFTWARE Research ideas engineered into future-proof software stacks. ... 2-10 employees. Headquarters: Vissenaken. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Qavis</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/qavis</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>koordinasyon, yazılım, veri analizi, kuantum, mobilite, rota ... software on Cray supercomputers. The big aerospace and automotive names used ...</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Enqura</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/enqura</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.enqura.com. External link for Enqura ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: London, ...</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>cognipeer</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/cognipeer</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: LONDON. Type ... ISTANBUL, TR. Get directions. DUSSELDORF, DE. Get directions. Employees at ...</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Overtech Information Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/overtech-information-technologies</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>... software departments and software houses of medium and large-scale institutions ... 11-50 employees. Headquarters: Başakşehir, İstanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Netmera</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/netmera</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>... Web Engagement, In-app Messaging, Customer Journeys, Mobile Push ... Similar pages. İnomera. Software Development. Istanbul, NA. Enqura. Software Development.</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Wipelot IoT</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://bw.linkedin.com/company/wipelot/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>... software systems, delivering technology-agnostic industrial IoT and real ... Istanbul, Istanbul. Deka Elektronik A.Ş. Appliances, Electrical, and ...</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Cybersoft North America Inc.</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cybersoft-north-america-inc-</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>... Software Solutions &amp; tools for multiple markets such as Artificial ... Web Applications, internet of things (IoT) and cross-platform Mobile ...</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Overteam</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/overteam</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, marmara. Type: Privately Held. Founded ... Project Manager | Web &amp; E-commerce |… Click here to view Tigran Apoyan's ...</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>51 DIGITAL</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/growth51</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>... Software as a Service platformumuz ve detaylı bilgi için team ... 51 DIGITAL, Istanbul, Istanbul, Türkiye. 21 1 Comment · Like Comment Share ...</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Tein Technology</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/company/solutions44</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>... Software Development in the area of Added Value Services, Test Engineering ... İstanbul Grand Pera'da gerçekleştirildi. TEİN Teknoloji olarak yer ...</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>ERC Group Engineering Consultancy and R&amp;D Services</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/ercgrup</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Çankaya, Ankara. Type: Privately Held. Specialties: Software Development, Healthcare Informatics, HIS, Software Research and ...</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Rollic</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://me.linkedin.com/company/rollic?trk=products_details_guest_organization_name</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul. Type: Privately Held. Specialties ... Fugo Games. Software Development. Istanbul, n/a. Show more similar pages. Show ...</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>TOLERANT Software GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/tolerant-software-gmbh-&amp;-co.-kg</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>http://www.tolerant-software.de. External link for TOLERANT Software GmbH &amp; Co. KG. Industry: Software Development. Company size: 11-50 employees. Headquarters ...</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>NanoSec Tech</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nanosec-tech</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2-10 employees. Type: Privately ... Similar pages. Nanosec. Defense and Space Manufacturing. Tradeware Teknoloji A.Ş. Software Development. Istanbul, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Altosec</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://bw.linkedin.com/company/altosec</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Altosec. IT Services and IT Consulting. Ankara, Ankara 567 followers. Altosec ... Software Development. Ankara, Çankaya · Baarne TAS. Information Services.</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Serkon Teknoloji</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/serkon-teknoloji/</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Website: http://www.serkon.ai. External link for Serkon Teknoloji ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: İstanbul ; Type ...</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Vector Group</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vector-barcode-&amp;-information-technology</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>VECTOR Information &amp; Software Technology is one of the leading information technologies, software ... 51-200 employees. Headquarters: Istanbul. Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Bilmed Bilgisayar ve Yazılım A.Ş.</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bilmed-bilgisayar-ve-yazilim-a-s-</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Bilmed Bilgisayar ve Yazılım A.Ş. | 686 followers on LinkedIn. Bilmed ... Software Development. Company size: 11-50 employees. Headquarters: İstanbul. Type ...</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Depixen</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://mt.linkedin.com/company/depixen-sw</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Eski Ankara Cad. No. 4/3-04 Çekmeköy. İstanbul, 34788, TR. Get directions ... software and AI teams Prior experience in data analytics or ontologies is not ...</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Unscrambl, Inc</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/unscrambl</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Atlanta, GA ... Ankara Teknoloji Geliştirme Bölgesi. Cyberpark Cyberplaza A Blok. Ankara ...</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D529"/>
+  <dimension ref="A1:D541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12066,6 +12066,270 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Alictus</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/alictus</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>... Web Analytics, Unity3D, Growth Hacking, Gaming, Web Applications ... Ankara, Ankara. Udo Games. Technology, Information and Internet. MildMania.</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Novit.AI</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/novitai</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://novit.ai. External link for Novit.AI ; Industry: Software Development ; Company size: 2-10 employees ; Headquarters: London ; Type ...</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>TimeInTech</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/timeintech</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2-10 employees ... Software Development. Istanbul, Istanbul · Soft Towel Games. Mobile Gaming Apps · BK Mobil. Information Technology &amp; Services. Ankara, Çankaya ...</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>ZETA DEFENCE</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/zetadefence</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>... software development, client-server architectures based on high performance ... 11-50 employees. Headquarters: İstanbul, Pendik. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>App Genie</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/appgco</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Software Development. Kadikoy, Istanbul. SevenApps. Software Development. İstanbul, Istanbul. Scate AI. Software Development. Şişli, Istanbul. Trendyol Group.</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>ECEMTAG Control Technologies</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/ecemtag?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Fatih Sultan Mehmet, Istanbul ... Software Engineer at ECEMTAG Control… See all ... Ankara, Çankaya · ARMELSAN. Defense &amp; Space.</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Havatech</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/havatech</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Havatech, as a software company, offers one of the finest ground handling software ... 11-50 employees. Headquarters: Asik Veysel, Istanbul. Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Hospitality Web</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/hospitalityweb</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>External link for Hospitality Web. Industry: Advertising Services. Company size: 2-10 employees. Headquarters: Al Nuzhah. Type: Privately Held. Founded: 2020.</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Zunilabs</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/zuni-games</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>About us. Zunilabs is a software technology company located in Kadıkoy, Istanbul. ... 2-10 employees. Headquarters: Fenerbahçe, Istanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Bilpp</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/bilppou</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>In addition to these, we are also leading in mobile application development, API integrations, custom solutions, and web applications. At Bilpp, it is our ...</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>ISITEC INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/isitec-international?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>11-50 employees ... Affiliated pages. AGV : Automated Guided Vehicle. Industrial Machinery Manufacturing. Isitrac, a software suite designed to optimize flow ...</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Kekik Teknoloji</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kekik</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees ... Beşiktaş, İstanbul · Çukurova Teknokent. Technology ... Botanik Yazılım Tic. Ltd. Şti. Software ...</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D541"/>
+  <dimension ref="A1:D546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12330,6 +12330,116 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>RFtek Electronics Ltd.</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rftek</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>RFtek Electronics was established in 2012 with the fund of Ministry of Science, Industry and Technology of Turkey. It is a startup company provides solution in various industries including medical ...</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Biotekno</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/biotekno</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Biotekno | 4,184 followers on LinkedIn. Mesajlaşma Servisleri ve Perakende Çözümleri | Kurulduğu 2003 yılından bu yana BİOTEKNO, uzman yazılım kadrosu, satış, iş geliştirme ...</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>serenity.is</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/serenity-is</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>We develop Serenity, which is an ASP.NET MVC / TypeScript application platform designed to simplify and shorten development of data-centric business applications with a service based architecture.</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Lucida AI</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/lucidaai</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Lucida AI Technology, Information and Internet London, England 17,164 followers Helping people and business teams speak languages with confidence.</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Koru Insurance Company Inc.</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/korusigorta/</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Koru Sigorta operates throughout Turkey with thousands of agencies and service points, backed by 15 years of insurance experience, sustainable growth targets, and a customer-focused approach ...</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D546"/>
+  <dimension ref="A1:D552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12440,6 +12440,138 @@
         </is>
       </c>
     </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Neon Apps</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neon-apps</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Neon Apps. Software Development. Sariyer, Istanbul 11,585 followers. We build mobile and web apps for startups and enterprises with an 85- ...</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Codeida</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/codeida</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: İstanbul, İstnabul ... Tepecik, Kocaeli. QReal. Advertising Services. New York, NY. Ekofin.net.</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>360 Company LLC</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/360-company-llc/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded: 2021. Products. No more previous content.</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>AIMultiple</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aimultiple</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>... software products for your business. ... Or just search: "AIMultiple ethical web scraping" and get the results for most web data providers.</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Raven Technology</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/raventechnology</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>... software licensing needs, innovate with new IT solutions and embrace the ... 11-50 employees. Headquarters: Istanbul, Beyoglu. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Smartin Information Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/smartin-information-technologies-ltd</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>... customly developed JEE solutions Developing the additional software that our customers need to achieve their business objectives.</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D552"/>
+  <dimension ref="A1:D562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12572,6 +12572,226 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Firmasoft</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>https://tt.linkedin.com/company/firmasoft-tech</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Istanbul, Kadıköy. Type: Public Company. Founded: 2004. Specialties: UI/UX Design, Web ...</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Univera</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/univeratechnology/</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>... software we produce at our R&amp;D Center, we offer solutions from A to Z for ... İstanbul akşamında bir araya gelerek sezona merhaba dedik. Bu özel geceye ...</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Ekip.co</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ekip-co</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Managed by gold-collar experts, Ekip is a network of elite software developers, graphic designers, project managers and digital marketing consultants.</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Senka Group</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>https://bw.linkedin.com/company/senka-group</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>... 2-10 employees. Headquarters: Gaborone, South-East. Type: Privately Held. Founded: 2018. Specialties: Software ... SAMSUN, Samsun · Klas Medical. Medical ...</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Weeb Group</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/weebgroup</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>İstanbul, İstanbul. Type: Privately Held. Founded: 2006. Specialties: c# , MVC, MSSQL, ADOBE, WEB TASARIM, GRAFIK TASARIM, Mobil Uygulamalar, weeb design, and ...</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Mobi Wan Digital Agency</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mobiwan</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, Beyoğlu. Type: Privately Held. Founded ... Software Development. GEBZE, KOCAELI · karbonat. Advertising Services.</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Dataroid</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dataroid</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Sariyer, Istanbul. Type: Privately Held. Specialties: data analytics, customer engagement ...</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>IPLUS Automation &amp; Software Solutions</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iplus-automation-software-solutions</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>About us. Industry: Software Development. Company size: 2-10 employees ... Ankara, Ankara · Novaco.tr. Wholesale Chemical and Allied Products. istanbul, istanbul ...</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Machinarium</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>https://az.linkedin.com/company/machinarium-technology?trk=public_profile_topcard-current-company</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul. Type: Public Company. Founded: 2021. Specialties: mobile, shopify, ios, android, react native, shopifyplus, and ...</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Mobilist</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mobilist</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Sarıyer, İstanbul. Type: Partnership. Founded: 2009. Specialties: Mobile, Cloud, Blockchain, MobileApp, Software Development, and ...</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D562"/>
+  <dimension ref="A1:D570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12792,6 +12792,182 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Talentics</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/talenticsapp?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Talentics is an innovative recruiting software and an HR tool that ... Software Development. Company size: 2-10 employees. Headquarters: Istanbul. Type ...</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Solvoyo</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solvoyo</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Boston, MA ... Maslak, Istanbul 34600, TR. Get directions. ITU Campus. ARI-2 Teknokent A ...</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>DevelopUs</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/developus-tr</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2-10 employees. Type: Privately Held. Employees at DevelopUs. Click ... Similar pages. DZD Teknoloji. IT Services and IT Consulting. Ataşehir, İstanbul, İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Byte</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bytedigitalcom/</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Byte. Software Development. Sisli, Istanbul 6,264 followers. Your Partner in the Digital Realm. Follow.</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>NOZZLE</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>https://me.linkedin.com/company/nozzle-ship-management-software/</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>About us · Website: http://www.nozzlesoft.com · Industry: Software Development · Company size: 11-50 employees · Headquarters: Istanbul, Ataşehir · Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Easy IT Consulting</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/easy-it-consulting/</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Brandium Residence R2 Blok K:20 Daire 247 Küçükbakkalköy / Ataşehir. Istanbul, Istanbul 34556, TR ... Software Engineer jobs. 300,699 open jobs · Intern jobs.</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>KBS Mobil</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kbs-mobil</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>KBS Mobil is a product built by a software team specialising in machine ... Similar pages. King's Labs. Software Development · The British School Istanbul.</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Simternet, Inc</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/simternet</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>... web and mobile based applications with more than 20 years of expertise ... Technology, Information and Internet. Istanbul, Istanbul. Ms. Chefs. Food and ...</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D570"/>
+  <dimension ref="A1:D582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12968,6 +12968,270 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Jengal Software</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jengal</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: KADIKÖY, İstanbul. Type: Privately Held. Founded: 2012. Specialties: Grafik Tasarım, Yazılım, Web, Reklam, and SEO. Locations.</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>IMMIB</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/immib/</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>IMMIB - Istanbul Minerals and Metals Exporters Association | 13,130 followers on LinkedIn. IMMIB is a non profit trade association affiliated to Ministry of Trade. The main goal of the association ...</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Istanbul Textile and Raw Materials Exporters Association ...</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ithib</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>About us Istanbul Textile and Raw Materials Exporters Association (ITHIB) is a leading entity representing the textile and raw materials exporters of Turkey with its members over 6000.</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Rivo Teknoloji A.Ş</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rivoteknoloji</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>External link for Rivo Teknoloji A.Ş Industry Appliances, Electrical, and Electronics Manufacturing Company size 51-200 employees Headquarters Çankaya, Ankara Type Privately Held Founded 2013 ...</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Fugo Games</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fugo-bili-im-teknolojileri</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Fugo Games | 21,441 followers on LinkedIn. Mobile Game Development Company | Mobile game development company, focused on casual / puzzle / word games, located in Istanbul / Turkey.</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Hudini</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mankaratechnologies</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Hudini elevates guest experience and boosts hotel revenues through end-to-end hospitality apps driven by data and AI. The proprietary omnichannel platform digitizes and connects every touchpoint ...</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Engageya</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/engageya</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Engageya (Engage Your Audience) offers a personalized &amp; semantic recommendation platform empowering networks with a private label native content &amp; advertising solution. Engageya’s native ads ...</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>CyberCube</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cybercube-analytics/</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>CyberCube | 15,001 followers on LinkedIn. Delivering data-driven cyber risk analytics for the insurance industry | CyberCube is delivering the world’s leading cyber risk modeling and analytics ...</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Shopier</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/shopier/</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Shopier Technology, Information and Internet Kadikoy, Istanbul 6,520 followers Your e-commerce! View all 171 employees</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Code And More</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>https://ke.linkedin.com/company/codeandmore1</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Code and More is a Software solutions company located in Istanbul. We specialized in: -Web Application -Mobile App Design and Development -CRM/Portal Design ...</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Anser Information Technologies</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ansertech</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Ankara, Çankaya · BARAKATECH. Software Development. Üniversiteler, Ankara · Antenom Antenna Technologies. Telecommunications. Ankara, Ankara · ANET Teknoloji A.</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Rgs Yazılım</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rgs-yaz%C4%B1l%C4%B1m-ve-bili%C5%9Fim-sistemleri</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Software Development. İstanbul, İstanbul 196 followers. Follow · Report this ... 11-50 employees. Headquarters: İstanbul, İstanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D582"/>
+  <dimension ref="A1:D585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13232,6 +13232,72 @@
         </is>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>MELASOFT</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/melasoft/</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Frankfurt, Hesse. Type: Privately Held. Founded: 2013. Specialties: SAP, ABAP, SAP Mobile, ...</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Demircode</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/demircode</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>... Web, Mobil ve Masaüstü platformlarında dijital ... Yazılım ... Kadikoy, Istanbul · Internative. Software Development. istanbul, Kadıköy. Show more similar pages</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>NOZZLE</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>https://zm.linkedin.com/company/nozzle-ship-management-software</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>About us · Website: http://www.nozzlesoft.com · Industry: Software Development · Company size: 11-50 employees · Headquarters: Istanbul, Ataşehir · Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D585"/>
+  <dimension ref="A1:D594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13298,6 +13298,204 @@
         </is>
       </c>
     </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Mobildev</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mobildev</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.mobildev.com. External link for Mobildev ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: İstanbul, ...</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>MagiClick Digital</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/magiclick-digital</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>... Istanbul &amp; Dubai, and we serve numerous multinational companies &amp; brands ... Software Development. City of London, England 18,132 followers. Leading ...</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>SIMULARGE Global</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/simularge</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>SIMULARGE Global. Software Development. PENDİK, İstanbul 4,310 followers. CAE and Digital Twin Solutions for productive and sustainable industries. Follow.</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Eteration</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/eteration</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Sarıyer ... Yazılım Geliştirme ve Modernizasyonu, Web Uygulama Geliştirme, Mobil ...</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Ploud</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>https://lv.linkedin.com/company/ploud</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>... Web/Mobile Applications. With its dynamic, young and qualified staff, Ploud challenges to all software ... 11-50 employees. Headquarters: Üsküdar, İstanbul.</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Kartaca</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/kartaca</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded: 2009. Specialties: php, java, mobile services, e-commerce solutions, omni- ...</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Dakik Yazılım</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dakikyazilim</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Dakik Yazılım. Software Development. HPC Çözümleri, BlockChain Çözümleri, MobiVisor - Mobil Cihaz Yönetimi (MDM, EMM).</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Algesoft</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/algesoft</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul. Type: Privately Held. Specialties: ai, nlp, blockchain, mobile development, aws, react-native, web-development, and ...</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Armut / HomeRun</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/armut</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Istanbul. Type: Privately Held. Locations. Primary. Acıbadem. Üsküdar. Istanbul, TR. Get ...</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D594"/>
+  <dimension ref="A1:D602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13496,6 +13496,182 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>SoftVerse</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/softverse</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Company size: 2-10 employees. Headquarters: Ankara. Type: Self-Employed. Founded: 2021. Specialties: software, iot, big data, r&amp;d, technology, metaverse, and ...</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Getek Yazılım</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getek-yaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>... web tabanlı erp sistemi tüm modül ve işlemlerin ... 2-10 employees ... Antalya, Antalya · Merlon. E-learning. Similar pages. WWWW. Software Development ...</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>AloTech</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/alotechbulut</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>... web based, pay-as-you-go solution running on Google, which is low cost, fast ... Istanbul, İstanbul · Turk Telekom. Telecommunications · LC Waikiki. Retail ...</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Syntonym</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/syntonym</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: London ... Istanbul, TR. Get directions. Employees at Syntonym. Click here to view Usluhan ...</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Biga Yazılım, Teknoloji ve Danışmanlık A.Ş.</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/biga-yaz%C4%B1l%C4%B1m-teknoloji-ve-dan%C4%B1%C5%9Fmanl%C4%B1k-a-%C5%9F</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2-10 employees. Type: Privately Held. Employees at Biga Yazılım, Teknoloji ... Istanbul, Istanbul · IAS - Industrial Application Software. IT Services and IT ...</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>HRweb Software</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hrwebsoftware</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>External link for HRweb Software. Industry: IT Services and IT Consulting. Company size: 11-50 employees. Headquarters: Durham, North Carolina. Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Statu</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/statu</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: San Francisco, California. Type: Privately Held. Founded: 2019. Specialties: Web Tasarımı, Web Yazılımı, and Arayüz Tasarımı ...</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>ICM Software</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/icm-software</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Software Development. Ankara, ANKARA · Web tasarım Hizmetleri. IT Services and IT Consulting. Ankara, yenimahalle · Unity Consultants Pvt. Ltd. Utilities ...</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D602"/>
+  <dimension ref="A1:D607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13672,6 +13672,116 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>WERARE</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/werare</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>WERARE is an award-winning software services company with a number of projects in the IT sector. ... 2-10 employees. Headquarters: İstanbul, Şişli. Type ...</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Kartaca</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kartaca</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>The mission is to democratize software with inquisitive and experimenting people and provide solutions for life. ... Istanbul, Istanbul 34220, TR. Get directions.</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Youthall</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/youthall</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Youthall Technology, Information and Internet Kadıköy, İstanbul 93,262 followers Raise employer brand awareness, show company culture and hire young talent.</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Intellica</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intellica</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Intellica is Big Data, Business Intelligence consultancy and software company that operates in more than 10 countries. Intellica is a expert company specialized on Business intelligence, Big data ...</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>EXENTECH</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/exentech</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>EXENTECH Defense and Space Manufacturing Yenimahalle, Ankara 3,324 followers Exclusive Engineering Follow Discover all 11 employees Report this company</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D607"/>
+  <dimension ref="A1:D610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13782,6 +13782,72 @@
         </is>
       </c>
     </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Aizona Tech</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aizona-tech</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Sisli, Istanbul. Type: Partnership. Locations ... Software Development. Istanbul, Istanbul. Morphy Capital. Financial Services ...</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>ADASTEC Corp.</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adastec</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 51-200 employees. Headquarters: East Lansing, Michigan.</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Rnv.ai</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rnv-analytics/?trk=products_details_guest_organization_page</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Software Development. İstanbul, Istanbul 5,361 followers. RNV Analytics is an ... Antalya, Antalya. Faik Sönmez. Textile Manufacturing. İstanbul, İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D610"/>
+  <dimension ref="A1:D617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13848,6 +13848,160 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Numesys</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/numesysilerimuhendislik</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Software Development. Only Certified Elite Channel Partner of Ansys in Turkey ... 🚀 Ansys EMEA Partner Yöneticisi Giampaolo Prada'yı Ankara ve İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>kloia</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/kloia</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>... Web Services (AWS) AWS Partners. No alternative text description for this ... Istanbul, TR. Parny. Software Development. Tmob AI Studio. IT Services and IT ...</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>CODEX</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/codex-yazilim</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>We're #hiring a new Senior Artificial Intelligence Software Engineer in Sariyer, Istanbul. ... We're #hiring a new Mobil Uygulama Geliştirici in Sarıyer, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Wipelot IoT</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>https://sz.linkedin.com/company/wipelot?trk=products_seo_search</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>About us · Website: http://www.wipelot.io · Industry: IT Services and IT Consulting · Company size: 51-200 employees · Headquarters: İstanbul · Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Chex</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chexplease</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://chex.com.tr. External link for Chex ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: İstanbul ; Type ...</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Dataroid</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>https://wk.linkedin.com/company/dataroid?trk=products_seo_search</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Sariyer, Istanbul ... Dogan Necip Mersin, Senior Executive Partner at Gartner Elif Acar Özgüner ...</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>UserMotion</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/usermotion</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Middletown, Delaware. Type: Public Company ... Lead Scoring Software. UserMotion is a sales intelligence platform that uses ...</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D617"/>
+  <dimension ref="A1:D628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14002,6 +14002,248 @@
         </is>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>taze</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/taze</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>İstanbul, Istanbul. Type: Privately Held. Founded: 2013. Specialties: Web Development, Frontend Development, Backend Development, Web Strategy, Mobile, Software ...</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Nuevo Softwarehouse</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>https://gh.linkedin.com/company/nuevo-softwarehouse</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Istanbul, YTU Teknopark Davutpaşa A1 Blok Z01 ... Software Developer. Click here to view Mustafa Yücedağ's profile. Mustafa ...</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Dataroid</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/dataroid</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Sariyer, Istanbul. Type: Privately Held. Specialties: data analytics, customer engagement ...</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Qpien</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/qpien?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>... web sitemiz üzerinden bizlere ulaşarak detaylı bilgi alabilirsiniz. ... İstanbul, Istanbul · Zagrose. Vähittäismyynti. Nashville, Tennessee · Apilex.</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Reseed Software</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/reseed-software</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>... web development, IT consulting, and custom software development. We are ... 2-10 employees. Headquarters: Liège. Type: Privately Held. Founded: 2024 ...</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>NGBS</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/ngbs-pvt-ltd</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>... software products, scale engineering capacity and move critical technology ... Web &amp; Mobile Product Engineering • Cloud &amp; DevOps • AI-enabled Solutions ...</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>TURBOARD</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/e-quality-software-llc</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: London, England. Type: Privately Held. Founded: 2004 ... Ankara, TR. neatCal. Software Development. Kırıkkale, Kırıkkale. Turkish ...</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>JobRunr</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/jobrunr</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>... Software Developer - Trendyol Group 🤖 Sıfırdan Yapay Zeka Tabanlı Seyahat ... yazılım dünyasındaki yenilikleri keşfederden ve networkünüzü genişletirken gün ...</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>HoloNext</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>https://lt.linkedin.com/company/holonext</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Vilnius. Type ... Developed as a web-based 3D application, it requires no download and ...</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Cognizen</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cognizen</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://www.cognizen.ai. External link for Cognizen ; Industry: Software Development ; Company size: 2-10 employees ; Type: Privately Held ...</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>RealWorks</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/realworksglobal</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Terminal İstanbul is taking shape as a new center for technology and ... web. 🌐 But in a world obsessed with talking, the ultimate competitive ...</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D628"/>
+  <dimension ref="A1:D641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14244,6 +14244,292 @@
         </is>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Macola Software</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/macola-software</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Macola Software | 489 followers on LinkedIn. Macola Software, an ECi Software ... Istanbul , Çengelköy. Tricorn Systems Ltd. Software Development. Horizon ERP.</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>PromoLink</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/promolinkcaa</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>The promo industry's software solution, built for suppliers, distributors ... 11-50 employees. Headquarters: San Tan Valley, AZ. Type: Self-Owned. Founded ...</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>ICRON</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/icron</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Amsterdam ... Software Development. Barcelona, Catalonia. Şişecam. Glass, Ceramics and Concrete Manufacturing. İstanbul, Tuzla ...</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Elratech</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/elratech</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Type: Privately Held. Founded: 2024. Specialties: software, on demand apps, web, IT, and AI. Employees at ...</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Steer73</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/steer73</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Similar pages. Steer Workplace (Formerly Evac One). Facilities Services · KCR Yazılım ve Danışmanlık. Software Development. Ankara, Ankara · 4A Labs. IT ...</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Continium Enterprise DevOps Services</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/continium-io</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Aim to build fast, robust and repeatable pipelines for error-free software development life cycle. ... Mobil imza Api / Web Servis ( eSignBox ). Information ...</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Gen10</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/generation-10-limited</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>ICA Istanbul ... Software Development. Stamford, CT. Commodity Trading Week. Events Services ...</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Webralli Managed Cloud Services</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>https://tt.linkedin.com/company/webralli</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Webralli Managed Cloud Services. Information Technology &amp; Services. Istanbul, Bahcelievler 18 followers. GO 123 | Get Google G Suite, web sites/apps ...</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Alpaco</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alpacotech</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Alpaco, Istanbul, Istanbul, Türkiye · 3 · Like Comment Share · Alpaco reposted this ... Web ve mobil ürünlerimiz için; - UI/UX Designer - Flutter Developer ...</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Penta Software &amp; Creative UK</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/penta-software-creative-uk-ltd</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>As Penta Software &amp; Creative, we comprise a distinguished team of web ... Similar pages. Penta Yazılım ve Ajans Hizmetleri. Software Development. Kartal, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>SoftAvail, Inc.</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/softavail-inc-</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 11-50 employees. Headquarters: San Carlos, California.</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Alictus</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/alictus</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: ANKARA, Cankaya. Type: Privately Held. Founded ... Web Analytics, Unity3D, Growth Hacking, Gaming, Web Applications ...</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Worktivity</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/worktivity</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Similar pages. Internative. Software Development. istanbul, Kadıköy. Lymo Games. Computer Games. Holacon. Software Development. Istanbul, kadıköy. Figensoft.</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D641"/>
+  <dimension ref="A1:D649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14530,6 +14530,182 @@
         </is>
       </c>
     </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Modelra</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/modelra-software/</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Industry: Software Development ; Company size: 2-10 employees ; Headquarters: Istanbul, Şişli ; Type: Privately Held ; Founded: 2022.</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>PoolText</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pooltext</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>We're #hiring a new Full Stack Engineer in Ankara, Ankara. Apply today or ... Istanbul, Istanbul. DataBoss Security &amp; Analytics A. Ş. Software ...</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Solveka</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solveka</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Website: http://www.solveka.com.tr. External link for Solveka ; Industry: Software Development ; Company size: 2-10 employees ; Headquarters: Çankaya, Ankara ; Type ...</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Basecope</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/basecope</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Website: https://basecope.com.tr/. External link for Basecope ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: Sariyer, Istanbul.</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>MGS Software</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mgs.software</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: istanbul, Başakşehir. Type: Public Company. Founded: 2017. Specialties: Web Application, ...</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Veloxity Inc.</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veloxity-inc-</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 11-50 employees. Headquarters: Maltepe / Istanbul, ...</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>AppNation</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/appnationco?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Website: https://appnation.co. External link for AppNation ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: Istanbul, Şişli ; Type ...</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>WebInStats</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/webinstats</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Istanbul, Istanbul. Type: Public Company. Founded: 2015. Specialties: Banner Management, ...</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D649"/>
+  <dimension ref="A1:D656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14706,6 +14706,160 @@
         </is>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Creas Technology Software &amp; Consulting</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cst-software-&amp;-consulting</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: ANKARA. Type: Privately Held. Founded: 2013 ... Similar pages. CREAS Bilişim Teknolojileri. Software Development. Mersin, Yenişehir ...</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>NextLua</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nextlua</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul, İstanbul. Type: Privately Held. Founded: 2017. Specialties: UX Design , UI Design, Webdevelopment, MobileDevelopment ...</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>epctex</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/epctex</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>epctex. Software Development. Istanbul, Beyoglu 1,185 followers. Data acquisition, at any scale. Follow.</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Armut / HomeRun</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/armut?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Istanbul. Type: Privately Held. Locations. Primary. Acıbadem. Üsküdar. Istanbul, TR. Get ...</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Kodzilla</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kodzillaistanbul</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>We build software solutions, backed by Web, Mobile, AR/VR/XR based ... Similar pages. Reaktor İstanbul. Advertising Services. İstanbul, Istanbul. Finderex.</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Abralabs Software Technologies</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/abralabs</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>... software technologies. Industry: Software Development. Company size: 11-50 employees. Headquarters: İSTANBUL. Type: Privately Held. Locations. Primary. İZZET ...</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>MikroKom Yazılım A.Ş.</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/mikrokom</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Software Development. Yenimahalle, Ankara ... 🚀 #Kalfa #Kalfa360 #MaliMüşavir #SMMM #Samsun #DijitalDönüşüm #YapayZeka Sicilmatik MikroKom Yazılım A.Ş.</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D656"/>
+  <dimension ref="A1:D659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14860,6 +14860,72 @@
         </is>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>ArtiSoft Yazilim Danismanlik ve Teknoloji</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/artisoft-yazilim-danismanlik-ve-teknoloji</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>ArtiSoft Yazilim Danismanlik ve Teknoloji. Software Development. Kocaeli, Gebze 403 followers. Sectoral &amp; Private Software Development Company. Follow.</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Cognitiwe</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/cognitiweai</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>11-50 employees ... Software Development. Istanbul, NA. Motiwe. IT Services and IT Consulting. İstanbul, ISTANBUL. manibux. Financial Services. ISTANBUL, ISTANBUL ...</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Vocaelis</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vocaelis</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Software Development. Atlanta, Georgia 268 followers. Vocaelis scales ... Similar pages. Lieva. Hospitals and Health Care. Ankara, Ankara · Pivony. Business ...</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D659"/>
+  <dimension ref="A1:D664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14926,6 +14926,116 @@
         </is>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Callwiser</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/callwiser</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2-10 employees. Type: Self-Employed. Founded: 2024. Specialties: AI, Hiring ... Istanbul, Istanbul. iliksoft. Software Development. ANKARA, ÇANKAYA. OSKA ...</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>RadiusAI</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/radius-ai</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Tempe ... Web Developer jobs. 39,398 open jobs · Staff System Engineer jobs. 6,694 open ...</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>OnlyJS Technology</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/onlyjs-technology</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Software Development. London, England 208 followers. Build everything with ... React Native ✓ Backend Technologies: Node.js,Nest.js,Laravel,Django,Flask ...</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Appcircle</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/appcircleio</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Dover ... İstanbul, Maslak. ANKASOFT. Software Development. HubX. Software Development. Remus ...</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>QHotelier</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/qhotelier</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Muratpaşa, Antalya. Type: Self-Owned. Founded ... We're #hiring a new Guest Experience &amp; AI Systems Manager in Antalya, Antalya.</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D664"/>
+  <dimension ref="A1:D676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15036,6 +15036,270 @@
         </is>
       </c>
     </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Rass Technology</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rasstechnology</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Esenler. Type: Privately Held. Founded ... Yazılım. Locations. Primary. Teknopark - Yıldız Teknik Üniversitesi Çifte ...</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Magis Technology</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/magis-technology</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>... Software Solutions, SW Testing &amp; QA, Managed ICT Services and Consultancy to ... 51-200 employees. Headquarters: ISTANBUL, ESENLER. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Exclion</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/exclion</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, Sarıyer. Type: Privately Held. Founded ... Software Development. San Francisco, California. adbreak. Advertising ...</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Dria</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dria-ai</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>11-50 employees. Type: Privately ... Similar pages. Clemta. Financial Services. Lewes, Delaware. Vircon Group. Software Development. İstanbul, İstanbul/Beyoğlu ...</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Good Job Games</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/goodjobgames</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded ... Software Engineer jobs. 59,663 open jobs · Artist jobs. 6,247 open jobs ...</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>CampusOnline</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/company/campusonlinecom</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Maltepe, Istanbul · Kolaytik. Business Consulting and Services. Antalya, Antalya · AtakLabs. Software Development. Şereflikoçhisar, Ankara · Bolat Tasarım Ve ...</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carla-car-rental</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>... software company and we fuel our growth through product differentiation and ... 51-200 employees. Headquarters: İstanbul-Üsküdar. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>GEOSYS GIS &amp; Consultancy Services</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/geosystr</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>... Istanbul, GEOSYS carry out its R&amp;D activities at METU Technopolis in Ankara - TURKEY ... Software Development. Cankaya, Ankara 2,583 followers. Location ...</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Solarian</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/company/solarian</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul. Type: Privately Held. Founded: 2017 ... Sizleri yeni web sitemizi keşfetmeye davet ediyoruz. https://lnkd.in ...</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Apliman</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/apliman</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Dubai. Type: Privately Held. Founded ... Web Development Intern jobs · Marketing Specialist jobs · Software Engineer Intern jobs.</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Rollic</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>https://bw.linkedin.com/company/rollic?trk=products_details_guest_organization_name</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul. Type: Privately Held. Specialties ... Fugo Games. Software Development. Istanbul, n/a. Show more similar pages. Show ...</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Zirve Yazılım</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/zirve-yazilim</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Müşterilerine daha iyi yazılımlar üretmek için çalışmalarına Ankara Bilkent ... Similar pages. TeamSystem Türkiye. Software Development. İstanbul, Sarıyer ...</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D676"/>
+  <dimension ref="A1:D683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15300,6 +15300,160 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>TRMiX Technology &amp; Software Solutions</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trmixcom</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>External link for TRMiX Technology &amp; Software Solutions. Industry: IT Services and IT Consulting. Company size: 11-50 employees. Headquarters: Ankara, Çankaya.</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Novosoft Yazılım AŞ</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/novosoft-com-tr</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Website: http://www.novosoft.com.tr. External link for Novosoft Yazılım AŞ ; Industry: Software Development ; Company size: 2-10 employees ; Headquarters: Kocaeli, ...</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>EVAM</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/evamtech</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 51-200 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded: 2015. Specialties: Complex Event ...</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Risk Software Technologies</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/riskturk</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>External link for Risk Software Technologies. Industry: Financial Services. Company size: 11-50 employees. Headquarters: İstanbul. Type: Public Company. Founded ...</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Veriport</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veriport</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>51-200 employees ... Enterprise Software Solutions, Business Intelligence Systems , and Operational Software Solutions. Locations. Primary. YTU Teknopark.</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Map Yazılım A.Ş.</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mapyaz%C4%B1l%C4%B1m</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>External link for Map Yazılım A.Ş. Industry: Strategic Management Services. Company size: 11-50 employees. Headquarters: Çankaya, Ankara. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Ones Technology</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onestechnology</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Ones Technology. Software Development. Ankara, Ankara 3,222 followers. more than one. See jobs Follow · Report this company; Close menu. View all 70 employees ...</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D683"/>
+  <dimension ref="A1:D689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15454,6 +15454,138 @@
         </is>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>LBSoft Bilişim ve Yazılım Teknolojileri Ltd. Şti.</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lbsoft-bili%C5%9Fim-ve-yaz%C4%B1l%C4%B1m-teknolojileri-ltd-%C5%9Fti</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Ankara, TR. Type: Self-Owned. Founded: 2023 ... We're #hiring a new AI Software Engineer in Ankara, Ankara. Apply today or ...</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Solon Software</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solon-software/</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>... yazılım şirketi olarak yola çıktığımızda, kalbimizde denizin sonsuzluğu kadar büyük bir inanç vardı. ... Affiliated pages. SolonPort Automation. Software ...</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Frank.</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/frankdigital</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 11-50 employees. Headquarters: İstanbul, Şişli.</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>OPTiiM</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/optiim</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>OPTiiM is a software and services company based in Istanbul, London, Dublin and Toronto. ... 51-200 employees. Headquarters: Istanbul, Sisli. Type: Partnership.</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Ruul</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ruul</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Malmö. Type: Privately Held. Founded: 2017 ... Istanbul, Istanbul 34475, TR. Get directions. Narva mnt 5. Tallinn, 10117, EE.</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Logan Software</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/logansw</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>About us ; Website: www.logansw.com. External link for Logan Software ; Industry: Information Services ; Company size: 2-10 employees ; Headquarters: Logan, UT.</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D689"/>
+  <dimension ref="A1:D695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15586,6 +15586,138 @@
         </is>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Brain Low</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/brainlowcode</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Software Development. Ankara, Please select a state. Brain Team Yazilim Teknolojileri Ltd. Technology, Information and Internet. İstanbul, İstanbul. Aniventi AŞ.</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>IB Group E</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ibgroupdev</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Software Development. Istanbul, Şişli 910 followers. IB Group E-Commerce | Mobile | Digital Transformation | Web Application Development | Automation ...</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>İnterkod BIM/Yazılım</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/interkod</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>External link for İnterkod BIM/Yazılım. Industry: Software Development. Company size: 2-10 employees. Headquarters: İstanbul. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>BOBU</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getbobu/</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://bobuschool.com/#. External link for BOBU ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: Istanbul ; Type ...</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>MNA</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mna-informatics</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>MNA | 112 followers on LinkedIn. Minds in Action / Miles in Action | MNA is a tech company founded in Istanbul ... software solution Miles from Sofico.</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Channelinker</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/channelinker</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: Clifton, New ... ISTANBUL, BESIKTAS 34340, TR. Get directions. Updates. View organization ...</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D695"/>
+  <dimension ref="A1:D700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15718,6 +15718,116 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Optiyol</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/optiyol</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>... software reduces transportation costs and improves visibility for logistics ... İstanbul, Kurtköy 34906, TR. Get directions. Dumlupinar Bulvari. No:280.</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Hardal</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/usehardal</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Remote, United States. Type: Public Company. Specialties: Web ... Istanbul, TR. Get directions.</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Keymate</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/keymateio</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Data Security Software Products. Keymate.io is a modern access governance ... Istanbul stage. Warm thanks to Kubernetes Community Days Istanbul team and ...</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Skyloop</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyloopc/</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>View organization page for Tech Istanbul. Tech Istanbul. 25,390 followers. 2mo ... Software Engineer Intern jobs. 1,941 open jobs · Full Stack Engineer jobs.</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Pargesoft</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/pargesoft</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>51-200 employees. Type: Privately Held. Founded: 2002. Products. No more previous content. Cosmo HR · Microsoft Dynamics 365 Business Central, Enterprise ...</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D700"/>
+  <dimension ref="A1:D709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15828,6 +15828,204 @@
         </is>
       </c>
     </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Loodos</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/loodos/</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul, Maslak. Type: Privately Held. Founded: 2004. Locations. Primary. Maslak Mah. Büyükdere Cad. Noramin İş Merkezi No:237/ ...</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Incotower</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/incotower</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Similar pages. PeopleBox. Software Development. İSTANBUL, KADIKÖY. BOARDIO ... BulutMD Yazılım. Software Development. Corlu, Tekirdag. Dream TV. Entertainment ...</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Key Software Solutions,Inc</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/key-software-solutions-inc</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Key Software Solutions,Inc | 692 followers on LinkedIn. Key Software Solutions ... Key Yazılım Çözümleri A.Ş. IT Services and IT Consulting. Ankara, Cankaya ...</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Heyhotel AI</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/heyhotelai</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>... web chat, and other digital channels. Employees at ... Markakod Reklam Tasarım ve Yazılım Hizmetleri. Technology, Information and Internet. İstanbul, Kadıköy ...</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>talp</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gettalp</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Website: https://talp.ai/. External link for talp ; Industry: Software Development ; Company size: 11-50 employees ; Headquarters: San Francisco, California ; Type ...</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>ERC Group Engineering Consultancy and R&amp;D Services</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>https://jm.linkedin.com/company/ercgrup</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Çankaya, Ankara. Type: Privately Held. Specialties: Software Development, Healthcare Informatics, HIS, Software Research and ...</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>mantis.group</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>https://cy.linkedin.com/company/mantis.group</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>... software and solutions vendor with European origins. With 9 offices and many ... 51-200 employees. Headquarters: Athens, Halandri. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Hirex</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gethirex</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Discover Hirex today! Website: https://gethirex.com/. External link for Hirex. Industry: Software Development. Company size: 11-50 employees ... Recruiting ...</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Assima</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/assima</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>... software - at the largest scale. Since 2002, we've helped the world's ... 51-200 employees. Headquarters: Atlanta, Georgia. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D709"/>
+  <dimension ref="A1:D735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16026,6 +16026,578 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>İO Yazılım Çözümleri</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/io-yaz-l-m-z-mleri</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>İO Yazılım Çözümleri | 12 followers on LinkedIn. İO Software Solutions is founded in August 2012 in İstanbul to provide advanced software solutions for ...</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Telenity</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/telenity</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.telenity.com. External link for Telenity ; Industry: Software Development ; Company size: 51-200 employees ; Headquarters: Istanbul, ...</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Arksoft</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/company/bennetts-technologies</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Industry: Software Development. Company size: 11-50 employees. Headquarters: Port Elizabeth, Eastern Cape. Type: Privately Held. Founded: 1994. Specialties ...</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Smartsis Bilgi Teknolojileri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>https://mt.linkedin.com/company/smartsis</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Smartsis Bilgi Teknolojileri A.Ş. | 422 followers on LinkedIn. Software Solutions Provider | B2B Software Development, Web ... 2-10 employees. Headquarters ...</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/co-one-co</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Software Development. London, England · Werover. Software Development. London, England · Onlayer. Technology, Information and Internet. Ankara, Ankara · Hardal.</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Skeyl</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/skeyl</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>... software. Website: https://skeyl.com. External link for Skeyl. Industry: IT Services and IT Consulting. Company size: 2-10 employees. Headquarters: Acibadem, ...</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Amani</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>https://jm.linkedin.com/company/amani-ai</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Karafakıoğlu Cd No:116, 34467 Sarıyer/İstanbul, Turkey. Istanbul, 34467, TR ... Software Development. San Francisco, California · Tarentum AI. Software ...</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>FreshSens</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/freshsens</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Ankara, Çankaya, TR. Get directions. Muğla, TR. Get directions. Employees at ... Software Development. Esenler, Istanbul · Mava. Software Development. Menteşe ...</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>AppsCon Software Services Ltd</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/appscon-ltd.</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>AppsCon Software Services Ltd | 112 followers on LinkedIn. AppsCon is a Gold Oracle Partner, operating in Istanbul and London. AppsCon was established in ...</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Extra360 Technology Solutions</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/extra360</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Software Development. The enterprise platform for loyalty, payments and ... İstanbul, Esentepe, TR. Get directions. Employees at Extra360 Technology ...</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Wixot</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/wixot</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>About us ; Website: http://www.wixot.com. External link for Wixot ; Industry: Computer Games ; Company size: 11-50 employees ; Headquarters: Istanbul ; Type ...</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>enpina</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/enpina</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>enpina. Software Development. Istanbul, Turkey 34 followers. Transforming digital complexity into focused solutions and tangible outcomes. Follow.</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>RAMSA DEFENCE &amp; AEROSPACE</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/ramsa-defence</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>With the recently established software unit within our own organization ... 51-200 employees. Headquarters: Ankara, Sincan,Malıköy Anadolu Osb Mah. Type ...</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Bilkon Ltd.</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>https://mt.linkedin.com/company/bilkon-ltd</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Software Development. Bilkom. Computers and Electronics Manufacturing. Muhtaroğlu Holding. Food and Beverage Manufacturing. İstanbul/Beşiktaş/Etiler, Istanbul ...</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>MIP</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/mip-ltd</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>... software solutions for the industry. Apart from providing ready-to-use CAD ... 11-50 employees. Headquarters: Tallinn, Harjumaa. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/i-amglobal</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: London, England. Type: Partnership. Founded: 1996 ... İstanbul, İstanbul. DesignUM. Design Services. Istanbul, Beykoz. kardesign.</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Willow Software</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/willow-software</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: London, East London. Type: Privately Held. Founded: 2020 ... Arniva Yazılım A.Ş. Software Development. Muğla/Marmaris, Ege · BiPOM ...</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>ADAMAPP</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/adamapp</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>About us. ADAMAPP is a passionate, dynamic, and award-winning software house with offices in London and Prague. ... 2-10 employees. Headquarters: Harrow ...</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>VOLE</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/vole-sports-social</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>VOLE. Software Development ... Berk Göl. See all employees. Similar pages. Sports Digitale. Broadcast Media Production and Distribution. İstanbul, İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>ALVEXIS</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/alvexis</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>... yazılım desteği • Satış süreçlerinde destek sunacağız. Hedefimiz ... Aviyonik Test ve Sertifikasyon Mühendisi. ALVEXIS, Ankara, Ankara, Türkiye · 9 ...</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Continuous Software</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/continuous-software-ltd</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Dublin, Dublin. Type: Privately Held. Founded ... (Istanbul). This event is powered by Continuous Software ...</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>AROX Bilişim Sistemleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/aroxbilisim</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>... software solutions such as iOS &amp; Android mobile applications, web solutions ... 11-50 employees. Headquarters: Atasehir, Istanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>ASIST</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/asist</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Schaerbeek, Brussels Region. Type: Privately Held. Founded: 1995. Specialties: Microsoft Partner Gold Software ... İstanbul, Turkey ...</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>crowdsol.</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/crowdsol</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: London. Type ... Istanbul, TR. Get directions. Employees at crowdsol. Click here to view ...</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Rollic</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>https://sz.linkedin.com/company/rollic?trk=products_details_guest_organization_name</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul. Type: Privately Held. Specialties: games, mobile games, mobil oyun, and gaming ... Software Development. Barcelona ...</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Globit Software Development Company</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>https://am.linkedin.com/company/globit-development-company</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Globit Software Development Company | 197 followers on LinkedIn. As a web ... 11-50 employees. Headquarters: Yerevan, Yerevan. Type: Self-Employed. Locations.</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D735"/>
+  <dimension ref="A1:D761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16598,6 +16598,578 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>TEOPS</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/teops</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>... software and designs are carried out. Website: https://teops.com.tr ... Ankara, Ankara · TİTRA. Defense and Space Manufacturing. Çankaya, Ankara · ANOVA ...</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>dNb Human Resources</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dnbik</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>dNb managed by professionals expertized in human resources, software consultancy ... 11-50 employees. Headquarters: İstanbul, Pendik. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Proto</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/proto-cx</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Waterloo ... web, then routes them to the right financial institution and regulator.</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>DSS Technology</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dss-technology</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded: 2001. Specialties: BusinessObjects, Cognos ...</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Kolaysoft Teknoloji A.Ş.</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/kolaysoftteknolojia.%C5%9F.?trk=similar-pages_result-card_full-click</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Industry: IT Services and IT Consulting. Company size: 51-200 employees. Headquarters: Ankara ...</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>eyeofG Technologies</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eyeofg-technologies</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: İstanbul, İstanbul. Type: Privately Held. Founded: 2017. Specialties: Products: Phoenix CMS for enterprises, Quantum Metric ...</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Duman Management Consultancy</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/duman-management-consultancy/</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Üsküdar, İstanbul. Type: Privately Held. Founded: 2014. Specialties: Executive Search, Leadership Development, Human Resources ...</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Acrome</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>https://sz.linkedin.com/company/acrome-robotics?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Sarıyer, İstanbul. Type: Privately Held. Founded ... Ankara University. If you work in control systems education or research ...</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Global IT International</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/global-it-int</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>... Istanbul, Global IT provides end to end expertise in cloud transformation ... - Advanced Coding: Support software development, code optimization and complex ...</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Juphy AI</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/juphy</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Software Development. Wilmington, Delaware 1,970 followers. AI Sales Rep ... Istanbul, Istanbul. Content Distribution Corp. Software Development. Seattle ...</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>MOBİLTEK</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/mobiltek-bilisim</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>... software. MOBILTEK, serves in the fields of GPS vehicle tracking ... Seyir Mobil. IT Services and IT Consulting. Kocaeli, Kocaeli/Derince. Show more ...</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Uniworks</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>https://sz.linkedin.com/company/uniworks</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Istanbul. Type: Privately Held. Founded ... Software Development, Live Stream, and Technologies for Trade Shows ...</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Thinkx Software</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>https://ug.linkedin.com/company/thinkxsoftware</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: kampala, central. Type: Privately Held. Founded: 2017. Specialties: software development, ...</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Acrome</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>https://sz.linkedin.com/company/acrome-robotics?trk=public_profile_experience-item_result-card_image-click</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Acrome. Robotics Engineering. Sarıyer, İstanbul 2,178 followers. Acrome is a worldwide provider of robotic experience with software &amp; hardware for academia ...</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Promena</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/promena-in</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Bengaluru, Karnataka. Type: Partnership. Founded: 2016. Specialties: Software Development, IOT, UI/UX Design, Web Design, IOS App ...</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Advanco SA</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/advanco-sa</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>The software is customized to suit current and future needs, while ... Şişli, Istanbul, TR. Get directions. 128 City Road. London, EC1V 2NX, GB. Get ...</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>PoiLabs</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/poilabs</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>... Istanbul Airport for making this possible. Give passengers a consistent ... Software Engineer jobs. 29,852 open jobs · Engineer jobs. 79,088 open jobs ...</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Softech</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/softech-lb</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>About us. Software Technology Solutions (Softech) is a leading IT company that focuses on providing high-quality web-based solutions intended for deployment on ...</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>HotelRunner</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/hotelrunner</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>... Software Partner, Agoda Strategic Partner, Oracle, Hotelbeds, trivago, and ... 51-200 employees. Headquarters: London, England. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Efabrika</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>https://pk.linkedin.com/company/efabrika</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul, Beyoglu. Type: Privately Held. Founded ... Software Development, Journalism, Travel Marketing, Travel, Content ...</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Yuppo</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/yuppo</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: London, England. Type: Privately Held. Founded ... Software Development. Barcelona, Catalonia · Woto. Technology, Information and ...</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Lookin</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/lookinapp</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: London ... İstanbul, Sariyer · AuctionNow. Internet Marketplace Platforms. Lahore, Pakistan ...</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>RentnConnect</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/rent-n-connect</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Istanbul, Istanbul. Shopney. Technology, Information and Internet. Los Angles ... Software Engineer jobs. 29,852 open jobs · Analyst jobs. 63,799 open jobs ...</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Saypr</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/saypr</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: London. Type: Privately Held. Founded: 2013. Specialties: Internet, Digital, Web, Product Design, Software Development, Agile ...</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Apliman</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/apliman</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Apliman | 20080 followers on LinkedIn. Smart Communication Solutions | Since 1994, Apliman has spearheaded software development and telecommunication ...</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Cremicro</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cremicro</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>... Web Design, Content Marketing, Lead Generation, Growth Marketing, Growth ... Istanbul, Istanbul · Sempeak. Advertising Services. Altunizade, İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D761"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17170,6 +17170,600 @@
         </is>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Synaps AI</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/synaps-artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>... software interviews Consistent scoring &amp; insights to reduce variability ... Ankara, Ankara. HiRi.ai. Software Development. SynapsAi. Information Services ...</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Rockville Technologies</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>https://pk.linkedin.com/company/rockville-technologies</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>... software development and telecom solution provider. We pride ourselves on a ... 51-200 employees. Headquarters: Islamabad, Federal. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Newployee</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>https://ee.linkedin.com/company/newployee</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>... software engages new hires, streamlines the onboarding process, and ... İstanbul, İstanbul · Onedio.com. Online Audio and Video Media. Ankara, Çankaya ...</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Techfinity</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/techfinity-ltd</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Cloud based Software-as-a-Service (Saas), Mobile Solutions, Remote Working ... Istanbul, Istanbul. Techfinity Solutions &amp; Research Center Pvt. Ltd. IT ...</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Orien</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/orien-app</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: South Brisbane, Queensland. Type ... IT System Custom Software Development. Istanbul, Esenler, Yıldız Teknik Üniversitesi ...</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Omtera</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/omtera</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: London. Type: Privately Held. Founded: 2019. Specialties: Asana, Mixpanel, Segment, ABTasty, Braze, Contentsquare, OneSignal ...</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>AWWCOR, Inc.</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/awwcor</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: Dover, Delaware. Type: Privately Held. Founded ... Close menu. Startups are hiring differently in 2026. 63,000+ software engineer ...</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Marksoft</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>https://am.linkedin.com/company/marksoftcompany</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Marksoft is a trusted technology partner specializing in innovative software solutions for banks and enterprises. ... 11-50 employees. Headquarters: Aygedzor ...</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>ACA Dijital Pazarlama</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/acadijitalpazarlama/</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Yakuplu, Istanbul. Type: Partnership. Founded: 2019. Specialties: SEO, Wordpress, Web Design, Digital Marketing, Keyword Analysis ...</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Generic Solutions</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/generic-solutions</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>... Software Solutions,EGovernment Solutions and Web Solutions across the globe. Industry: Software Development. Company size: 11-50 employees. Headquarters ...</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Producter</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/producter</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://producter.co. External link for Producter ; Industry: Software Development ; Company size: 2-10 employees ; Headquarters: Remote ; Type ...</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Tulip Web Solutions</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/tulip-web-solutions</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>External link for Tulip Web Solutions. Industry: IT Services and IT Consulting. Company size: 2-10 employees. Headquarters: Rotterdam. Type: Self-Owned. Founded ...</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Pragma</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/pragma_3?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Pragma Bilisim Yazilim Danismanlik Tic. Ltd. Sti. is a software ... software for its customers. ... 2-10 employees. Päätoimipaikka: Istanbul, Istanbul. Tyyppi ...</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Verikar</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>https://ng.linkedin.com/company/verikar</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Similar pages. ISEF Bilgi Teknolojileri. Information Technology &amp; Services. Kurtköy, İstanbul · Verikai. Software Development. San Francisco, California ...</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Mobirun</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>https://me.linkedin.com/company/mobirunco</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees. Headquarters: Budva. Type ... Similar pages. Tamyeri Dijital Ajans. Software Development. istanbul, Üsküdar ...</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Pure New Media</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>https://za.linkedin.com/company/pure-new-media</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, Karaköy / Beyoğlu. Type ... Similar pages. Co.Brand. Advertising Services. İstanbul, Besiktaş · Hopi. Software ...</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Insight Data Danışmanlık</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/insight-data-dan%C4%B1%C5%9Fmanl%C4%B1k</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Ankara. Type: Self ... Etimesgut, Ankara · Ekin Danışmanlık ... Browse jobs. Analyst jobs. 694,057 open jobs · Software Support jobs.</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>adindie</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/.adindie</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Mobil oyunlar ve VR deneyimleri üstüne ... 11-50 employees. Headquarters: Kocaeli, Kocaeli ... Locations. Primary. 28 Haziran Mah. Eski İstanbul Yolu Cad.</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Abra Danışmanlık</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/abradan?trk=ppro_cprof</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Şişli, Istanbul. Type: Partnership. Founded ... Software Development. Istanbul, Beşiktaş · EVAM. Software Development. Istanbul, ...</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>TerraByte</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/terrabytebr</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 2-10 employees ... Similar pages. Terrabyte. Technology, Information and Media. Omaha, Nebraska · İstanbul Business School ( ...</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Marka Liman</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/markaliman</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>... Web sitesi - Sosyal Medya Strateji ve Hesap ... 2-10 employees. Headquarters: Kadıköy, İstanbul ... Egeria Software. IT Services and IT Consulting. İZMİR ...</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>CRM RedWhite</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/redwhitecrm</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>... yazılım alt yapısı ve şık tasarımı ile ... 11-50 employees ... Similar pages. CRM KURUMSAL İŞ ÇÖZÜMLERİ DANIŞMANLIK. Software Development. İstanbul, İstanbul / ...</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Türkçe Terapi</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/company/t%C3%BCrk%C3%A7e-terapi</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>2-10 employees. Päätoimipaikka: İstanbul, İstanbul ... Heryer Online Yazılım. Ohjelmistokehitys. ankara, türkiye ... Istanbul, Maslak · Spring Health.</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>hadi</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>https://pk.linkedin.com/company/hadi-live-games?trk=public_profile_experience-item_profile-section-card_subtitle-click</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: istanbul , istanbul. Type: Privately Held. Founded ... Software Development. İstanbul, Üsküdar. Show more similar pages. Show ...</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Senkron Güvenlik ve İletişim Sistemleri A.Ş.</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/senkron-g-venlik?trk=public_profile_experience-item_result-card_image-click</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>51-200 employees. Headquarters: İstanbul, Şişli ... Ankara, Balgat - Çankaya 06520, TR ... Similar pages. Senkron Tech. Software Development. İstanbul, Esenler ...</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>OwlIO</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/owlionet/</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Dubai, Dubai. Type: Partnership. Founded: 2023. Specialties: web development, cyber security, Mobile app development, Penetration ...</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>OSGBM</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osgb-merkezi</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, Küçükçekmece. Type: Partnership. Founded: 2015. Specialties: internet, yazılım, bilgi teknolojileri, mobil, insan ...</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17764,6 +17764,72 @@
         </is>
       </c>
     </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>MGS Software</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/mgs.software</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: istanbul, Başakşehir. Type: Public Company. Founded: 2017. Specialties: Web Application, ...</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Karash Software Ltd.</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/karash-software&amp;security-technologies</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul ... Karash Software Ltd. MICROSOFT DYNAMICS AX (AXAPTA) ERP UZMANI. Karash Software Ltd., Istanbul, Istanbul, Türkiye.</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>VARIIN</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/variin</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Website: variin.com. External link for VARIIN ; Industry: IT System Custom Software Development ; Company size: 2-10 employees ; Headquarters: Çankaya, Ankara.</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17830,6 +17830,160 @@
         </is>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>PXL Digital Solutions</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pxldigitalsolutions</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>PXL Digital Solutions. Software Development. Istanbul, Üsküdar 3,286 followers. Transforming Ideas Into Digital Solutions. Follow.</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Aniventi AŞ</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>https://zw.linkedin.com/company/aniventias</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Ankara, Çankaya. Type: Privately Held. Founded: 2018. Specialties: Software, IoT, Project Management, International Markets ...</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Monad Yazılım ve Danışmanlık</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/monad-yazilim</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Monad Yazılım ve Danışmanlık. Software Development. Ankara, Ankara 3,303 followers. Sağlık yazılımında etkin proje yönetimi ve güçlü destek yaklaşımı. Follow.</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Arge360 Yazılım Teknolojileri</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arge360-yaz%C4%B1l%C4%B1m-teknolojileri</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>External link for Arge360 Yazılım Teknolojileri. Industry: Software Development. Company size: 11-50 employees. Headquarters: İstanbul, Şişli. Type: Privately ...</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Sigun Information Technologies and Consultancy</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sigun-bilgi-teknolojileri-ve-dan%C4%B1%C5%9Fmanl%C4%B1k-a-%C5%9F-</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Ankara, Ankara. Type: Public Company. Founded: 2014. Specialties: Yazılım Geliştirme, Büyük Veri Sistemleri, Modelleme ve ...</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Next4biz</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/next4biz</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>... | 32381 followers on LinkedIn. AI Powered Customer Service Software ... Canlı sohbet, WhatsApp ve mobil uygulama üzerinden benzer sorular peş peşe geliyor: 🔻 ...</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Liquidity Trading</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/liquidity-trading/</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul. Type: Privately Held. Founded: 2020 ... Software Development. Istanbul, Istanbul. Bull Teknoloji. IT Services and IT ...</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17984,6 +17984,94 @@
         </is>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Monovi Information Technology A.S.</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/monovi/</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Software Development, Agile, Business Analysis, Transportation Management System, Mobile App Development, Web ... Siskon Yazılım &amp; Otomasyon. Software ...</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>HEPAPI</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/hepapi</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>... Web Services (AWS), Google Cloud Platform, Microsoft Azure, Kubernetes ... Istanbul, TR. Get directions. 284 Chase Road. London, England N14 6HF, GB. Get ...</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Orkan Software</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/orkan-software</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Orkan Software | 20 followers on LinkedIn. Founded in 2014, Orkan Software ... 2-10 employees. Headquarters: ISTANBUL, KAGITHANE. Type: Privately Held. Founded ...</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>ATEZ</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/atezsoftware</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>ATEZ Software Technologies is a forward‑looking technology company ... İstanbul, Istanbul. Kafein Technology Solutions. Software Development. İstanbul ...</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18072,6 +18072,160 @@
         </is>
       </c>
     </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>iyosa</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iyosa</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>About us ; Website: https://iyosa.com/. External link for iyosa ; Industry: Software Development ; Company size: 2-10 employees ; Type: Privately Held ; Founded ...</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>ONFTECH</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onftech</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Financial Risk Management Software. TWG (Tanfeeth Watheeq Gateway) is an AI ... Istanbul, Istanbul, TR. Get directions. Employees at ONFTECH. Click here to ...</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>OneSec</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onesecdelivery</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>2-10 employees. Headquarters: Zurich. Type: Privately Held. Founded: 2020 ... Senior Software Engineer Team Lead jobs · Computer Engineer jobs · Information ...</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Kolay İK</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/company/kolayik?trk=public_profile_experience-item_profile-section-card_image-click</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Kolay İK. Software Development. Kadiköy, İstanbul 55,969 followers. Kolay helps the world's leading companies manage their HR management tasks across devices.</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>TÜMSAŞ AŞ</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/company/tumsas-a-s-</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>We provide end-to-end custom software and hardware development, project management, installation and after-sales support. From our Istanbul headquarters, ...</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>EyeCheckup</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/eyecheckup</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Software Development. Company size: 11-50 employees. Headquarters: London ... Ankara Onkoloji Hastanesi, Gülhane Eğitim ve Araştırma Hastanesi, and Van ...</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>YEPZ</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/yepz</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Cankaya, Ankara. Type: Privately Held. Specialties ... Software Development. Çankaya, Ankara · Codeway. Software Development.</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18226,6 +18226,50 @@
         </is>
       </c>
     </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Overtech Information Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/overtech-information-technologies</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>... software departments and software houses of medium and large-scale institutions ... 11-50 employees. Headquarters: Başakşehir, İstanbul. Type: Privately Held.</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Dengage</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/dengage</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>... web push, and on-site messaging. 3. AI-Driven Intelligence: Zeki AI Our ... Istanbul, Istanbul. Insider One. Software Development. Motive. Software ...</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18270,6 +18270,50 @@
         </is>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/superagency-istanbul</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Website: http://www.super-agency.com. External link for Super-Agency ; Industry: Advertising Services ; Company size: 11-50 employees ; Headquarters: Istanbul.</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Corbone Innovations &amp; Technologies</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corbonegroup</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: İstanbul, Sarıyer. Type: Partnership. Founded: 2012 ... Software Development, Health Ecosystems, Insurance Ecosystems ...</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hedef_sirketler.xlsx
+++ b/hedef_sirketler.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18314,6 +18314,50 @@
         </is>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>FanSupport</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fansupport</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>11-50 employees. Headquarters: Istanbul. Type: Privately Held. Founded: 2020 ... Software Development. ISTANBUL, ATAŞEHİR. TRANGELS. Venture Capital and Private ...</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>mindif AI</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/mindif</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Student | Software Developer. See all employees. Similar pages. Finever. IT Services and IT Consulting · TOM. Financial Services. Üsküdar, İstanbul ... Mersin, ...</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>İncelenmedi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
